--- a/MAESTRIA/Analisis Estructural Lineal y no Lineal/ASIGNAICON 2/Marlon Ivan Carreto Rivera, Analisis matricial Asignacion 2,.xlsx
+++ b/MAESTRIA/Analisis Estructural Lineal y no Lineal/ASIGNAICON 2/Marlon Ivan Carreto Rivera, Analisis matricial Asignacion 2,.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitdocs-2026\MAESTRIA\Analisis Estructural Lineal y no Lineal\ASIGNAICON 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitdocs-2026\MAESTRIA\Analisis Estructural Lineal y no Lineal\ASIGNAICON 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6905824A-DE52-4604-95F1-694742D51BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399615D9-75E0-4FB6-8F11-CBDE479B857A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7F94BADD-C052-4D7B-975E-F0C8373E1FC8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7F94BADD-C052-4D7B-975E-F0C8373E1FC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="67">
   <si>
     <t xml:space="preserve">EJEMPLO DE ANALISIS MATRICIAL DE UN MARCO CON VIGA COLUMNA BIDIMENSIONAL </t>
   </si>
@@ -206,6 +206,27 @@
   <si>
     <t>ELEMENTO 2, COLUMNA</t>
   </si>
+  <si>
+    <t>MATRIZ DE RIGIDEZ LOCAL DEL ELEMENTO 2</t>
+  </si>
+  <si>
+    <t>MATRIZ DE RIGIDEZ GLOBAL DEL ELEMENTO 2</t>
+  </si>
+  <si>
+    <t>ELEMENTO 3, COLUMNA</t>
+  </si>
+  <si>
+    <t>cm4</t>
+  </si>
+  <si>
+    <t>MATRIZ DE RIGIDEZ LOCAL DEL ELEMENTO 3</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>MATRIZ DE RIGIDEZ GLOBAL DEL ELEMENTO 3</t>
+  </si>
 </sst>
 </file>
 
@@ -355,22 +376,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -729,6 +750,162 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3370175" cy="2047875"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{699B447C-79BB-430A-BB7C-E0DCC12A3131}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5875194" y="13688291"/>
+          <a:ext cx="3370175" cy="2047875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>409576</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1426152" cy="1574853"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13C3F0BF-8939-49FB-9AFD-20D7C1A0B4FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3706958" y="13773150"/>
+          <a:ext cx="1426152" cy="1574853"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>328332</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>183216</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1648055" cy="1181265"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77177066-B203-487D-9FAA-E20CBF9A102D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8682623" y="17861616"/>
+          <a:ext cx="1648055" cy="1181265"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4839619" cy="1514475"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9B7B919-A65E-4336-8492-D3C3D0A12E3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6160943" y="19224047"/>
+          <a:ext cx="4839619" cy="1514475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1029,49 +1206,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6EEF42-2ACD-482D-8DFE-3F8C8E9FC543}">
-  <dimension ref="A1:AB144"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB216"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1"/>
-    <col min="2" max="2" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="11.44140625" style="1"/>
+    <col min="2" max="2" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="1"/>
+    <col min="10" max="10" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1082,7 +1259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1094,7 +1271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1102,10 +1279,10 @@
         <v>400</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1117,12 +1294,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1134,7 +1311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1146,7 +1323,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1158,7 +1335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1170,7 +1347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1182,10 +1359,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>17</v>
       </c>
@@ -1196,7 +1373,7 @@
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -1219,7 +1396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -1243,12 +1420,12 @@
       <c r="G19" s="7">
         <v>0</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -1274,10 +1451,10 @@
         <f>+C13</f>
         <v>267114.00008234923</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -1303,10 +1480,10 @@
         <f>+C15</f>
         <v>35615200.010979898</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -1330,10 +1507,10 @@
       <c r="G22" s="9">
         <v>0</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -1359,10 +1536,10 @@
         <f>-C13</f>
         <v>-267114.00008234923</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -1388,10 +1565,10 @@
         <f>C14</f>
         <v>71230400.021959797</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>25</v>
       </c>
@@ -1405,27 +1582,27 @@
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16" t="s">
+      <c r="F27" s="17"/>
+      <c r="G27" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16" t="s">
+      <c r="H27" s="17"/>
+      <c r="I27" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="J27" s="16"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
@@ -1461,7 +1638,7 @@
         <v>341905.92010540701</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -1498,7 +1675,7 @@
         <v>1335.5700004117459</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
@@ -1535,7 +1712,7 @@
         <v>71230400.021959797</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
@@ -1567,7 +1744,7 @@
         <v>-267114.00008234923</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>4</v>
       </c>
@@ -1597,7 +1774,7 @@
         <v>-267114.00008234923</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>18</v>
       </c>
@@ -1620,7 +1797,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="str">
         <f t="array" ref="A37:A42">+TRANSPOSE(B36:G36)</f>
         <v>1x</v>
@@ -1647,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="str">
         <v>1z</v>
       </c>
@@ -1673,7 +1850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="str">
         <v>ϴ 1</v>
       </c>
@@ -1699,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="str">
         <v>ax</v>
       </c>
@@ -1722,7 +1899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="str">
         <v>az</v>
       </c>
@@ -1745,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="str">
         <v>ϴ a</v>
       </c>
@@ -1768,94 +1945,94 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H45" s="18" t="s">
+      <c r="H45" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I45" s="18" t="s">
+      <c r="I45" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="J45" s="18" t="s">
+      <c r="J45" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="K45" s="18" t="s">
+      <c r="K45" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="L45" s="18" t="s">
+      <c r="L45" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="M45" s="18" t="s">
+      <c r="M45" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N45" s="18" t="s">
+      <c r="N45" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="O45" s="18" t="s">
+      <c r="O45" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="P45" s="18" t="s">
+      <c r="P45" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="Q45" s="18" t="s">
+      <c r="Q45" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="R45" s="18" t="s">
+      <c r="R45" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="S45" s="18" t="s">
+      <c r="S45" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="T45" s="18" t="s">
+      <c r="T45" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="U45" s="18" t="s">
+      <c r="U45" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="V45" s="18" t="s">
+      <c r="V45" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="W45" s="18" t="s">
+      <c r="W45" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="X45" s="18" t="s">
+      <c r="X45" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="Y45" s="18" t="s">
+      <c r="Y45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Z45" s="18" t="s">
+      <c r="Z45" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="AA45" s="18" t="s">
+      <c r="AA45" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="AB45" s="18" t="s">
+      <c r="AB45" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="str">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="str">
         <f t="array" ref="A46:A72">TRANSPOSE(B45:AB45)</f>
         <v>1x</v>
       </c>
@@ -1942,8 +2119,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="str">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A47" s="13" t="str">
         <v>1z</v>
       </c>
       <c r="B47" s="1">
@@ -2028,8 +2205,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="str">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="str">
         <v>ϴ 1</v>
       </c>
       <c r="B48" s="1">
@@ -2114,8 +2291,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="str">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="str">
         <v>2x</v>
       </c>
       <c r="B49" s="1">
@@ -2200,8 +2377,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="str">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A50" s="13" t="str">
         <v>2z</v>
       </c>
       <c r="B50" s="1">
@@ -2286,8 +2463,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A51" s="18" t="str">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A51" s="13" t="str">
         <v>ϴ 2</v>
       </c>
       <c r="B51" s="1">
@@ -2372,8 +2549,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A52" s="18" t="str">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A52" s="13" t="str">
         <v>3x</v>
       </c>
       <c r="B52" s="1">
@@ -2458,8 +2635,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A53" s="18" t="str">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A53" s="13" t="str">
         <v>3z</v>
       </c>
       <c r="B53" s="1">
@@ -2544,8 +2721,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="str">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A54" s="13" t="str">
         <v>ϴ 3</v>
       </c>
       <c r="B54" s="1">
@@ -2630,8 +2807,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="str">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A55" s="13" t="str">
         <v>4x</v>
       </c>
       <c r="B55" s="1">
@@ -2716,8 +2893,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="str">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="str">
         <v>4z</v>
       </c>
       <c r="B56" s="1">
@@ -2802,8 +2979,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="str">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A57" s="13" t="str">
         <v>ϴ 4</v>
       </c>
       <c r="B57" s="1">
@@ -2888,8 +3065,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="str">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="str">
         <v>5x</v>
       </c>
       <c r="B58" s="1">
@@ -2974,8 +3151,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A59" s="18" t="str">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A59" s="13" t="str">
         <v>5z</v>
       </c>
       <c r="B59" s="1">
@@ -3060,8 +3237,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A60" s="18" t="str">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A60" s="13" t="str">
         <v>ϴ 5</v>
       </c>
       <c r="B60" s="1">
@@ -3146,8 +3323,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="str">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A61" s="13" t="str">
         <v>6x</v>
       </c>
       <c r="B61" s="1">
@@ -3232,8 +3409,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A62" s="18" t="str">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A62" s="13" t="str">
         <v>6z</v>
       </c>
       <c r="B62" s="1">
@@ -3318,8 +3495,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="str">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A63" s="13" t="str">
         <v>ϴ 6</v>
       </c>
       <c r="B63" s="1">
@@ -3404,8 +3581,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A64" s="18" t="str">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A64" s="13" t="str">
         <v>ax</v>
       </c>
       <c r="B64" s="1">
@@ -3490,8 +3667,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A65" s="18" t="str">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A65" s="13" t="str">
         <v>az</v>
       </c>
       <c r="B65" s="1">
@@ -3576,8 +3753,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A66" s="18" t="str">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A66" s="13" t="str">
         <v>ϴ a</v>
       </c>
       <c r="B66" s="1">
@@ -3662,8 +3839,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A67" s="18" t="str">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A67" s="13" t="str">
         <v>bx</v>
       </c>
       <c r="B67" s="1">
@@ -3748,8 +3925,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A68" s="18" t="str">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A68" s="13" t="str">
         <v>bz</v>
       </c>
       <c r="B68" s="1">
@@ -3834,8 +4011,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A69" s="18" t="str">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A69" s="13" t="str">
         <v>ϴ b</v>
       </c>
       <c r="B69" s="1">
@@ -3920,8 +4097,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A70" s="18" t="str">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A70" s="13" t="str">
         <v>cx</v>
       </c>
       <c r="B70" s="1">
@@ -4006,8 +4183,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A71" s="18" t="str">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A71" s="13" t="str">
         <v>cz</v>
       </c>
       <c r="B71" s="1">
@@ -4092,8 +4269,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A72" s="18" t="str">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A72" s="13" t="str">
         <v>ϴ c</v>
       </c>
       <c r="B72" s="1">
@@ -4178,21 +4355,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A75" s="13" t="s">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A75" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>2</v>
       </c>
@@ -4203,7 +4380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -4212,10 +4389,10 @@
         <v>32552.083333333332</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
@@ -4226,7 +4403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>4</v>
       </c>
@@ -4238,12 +4415,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
         <v>8</v>
       </c>
@@ -4255,7 +4432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>9</v>
       </c>
@@ -4267,7 +4444,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>10</v>
       </c>
@@ -4279,7 +4456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>11</v>
       </c>
@@ -4291,7 +4468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
         <v>12</v>
       </c>
@@ -4303,12 +4480,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C88" s="4"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -4317,32 +4494,33 @@
       <c r="F89" s="15"/>
       <c r="G89" s="15"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>19</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="str">
+        <f t="array" ref="A91:A96">TRANSPOSE(B90:G90)</f>
+        <v>2x</v>
       </c>
       <c r="B91" s="6">
         <f>+C83</f>
@@ -4364,14 +4542,14 @@
       <c r="G91" s="7">
         <v>0</v>
       </c>
-      <c r="H91" s="17" t="s">
+      <c r="H91" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I91" s="17"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="5" t="s">
-        <v>20</v>
+      <c r="I91" s="16"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="str">
+        <v>2z</v>
       </c>
       <c r="B92" s="6">
         <v>0</v>
@@ -4395,12 +4573,12 @@
         <f>+C85</f>
         <v>267114.00008234923</v>
       </c>
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
-        <v>21</v>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="str">
+        <v>ϴ 2</v>
       </c>
       <c r="B93" s="6">
         <v>0</v>
@@ -4424,12 +4602,12 @@
         <f>+C87</f>
         <v>35615200.010979898</v>
       </c>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="s">
-        <v>22</v>
+      <c r="H93" s="16"/>
+      <c r="I93" s="16"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="str">
+        <v>bx</v>
       </c>
       <c r="B94" s="8">
         <f>-C83</f>
@@ -4451,12 +4629,12 @@
       <c r="G94" s="9">
         <v>0</v>
       </c>
-      <c r="H94" s="17"/>
-      <c r="I94" s="17"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>23</v>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="str">
+        <v>bz</v>
       </c>
       <c r="B95" s="8">
         <v>0</v>
@@ -4480,12 +4658,12 @@
         <f>-C85</f>
         <v>-267114.00008234923</v>
       </c>
-      <c r="H95" s="17"/>
-      <c r="I95" s="17"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
-        <v>24</v>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="str">
+        <v>ϴ b</v>
       </c>
       <c r="B96" s="8">
         <v>0</v>
@@ -4509,12 +4687,12 @@
         <f>C86</f>
         <v>71230400.021959797</v>
       </c>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H96" s="16"/>
+      <c r="I96" s="16"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="15" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -4526,27 +4704,27 @@
       <c r="I98" s="15"/>
       <c r="J98" s="15"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
-      <c r="C99" s="16" t="s">
+      <c r="C99" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D99" s="16"/>
-      <c r="E99" s="16" t="s">
+      <c r="D99" s="17"/>
+      <c r="E99" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F99" s="16"/>
-      <c r="G99" s="16" t="s">
+      <c r="F99" s="17"/>
+      <c r="G99" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H99" s="16"/>
-      <c r="I99" s="16" t="s">
+      <c r="H99" s="17"/>
+      <c r="I99" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="J99" s="16"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J99" s="17"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>30</v>
       </c>
@@ -4582,7 +4760,7 @@
         <v>341905.92010540701</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>31</v>
       </c>
@@ -4619,7 +4797,7 @@
         <v>1335.5700004117459</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>32</v>
       </c>
@@ -4656,7 +4834,7 @@
         <v>71230400.021959797</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4" t="s">
@@ -4688,7 +4866,7 @@
         <v>-267114.00008234923</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C104" s="4" t="s">
         <v>4</v>
       </c>
@@ -4718,33 +4896,34 @@
         <v>-267114.00008234923</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B108" s="5" t="str">
+        <f t="array" ref="B108:G108">B90:G90</f>
+        <v>2x</v>
+      </c>
+      <c r="C108" s="5" t="str">
+        <v>2z</v>
+      </c>
+      <c r="D108" s="5" t="str">
+        <v>ϴ 2</v>
+      </c>
+      <c r="E108" s="5" t="str">
+        <v>bx</v>
+      </c>
+      <c r="F108" s="5" t="str">
+        <v>bz</v>
+      </c>
+      <c r="G108" s="5" t="str">
+        <v>ϴ b</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="str">
         <f t="array" ref="A109:A114">+TRANSPOSE(B108:G108)</f>
-        <v>1x</v>
+        <v>2x</v>
       </c>
       <c r="B109" s="6">
         <f>(J100*B102*B102)+(J101*B101*B101)</f>
@@ -4768,9 +4947,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="str">
-        <v>1z</v>
+        <v>2z</v>
       </c>
       <c r="B110" s="6">
         <f>(J100-J101)*B102*B101</f>
@@ -4794,9 +4973,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="str">
-        <v>ϴ 1</v>
+        <v>ϴ 2</v>
       </c>
       <c r="B111" s="6">
         <f>-J104*B101</f>
@@ -4820,9 +4999,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="str">
-        <v>ax</v>
+        <v>bx</v>
       </c>
       <c r="B112" s="8">
         <v>0</v>
@@ -4843,9 +5022,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="str">
-        <v>az</v>
+        <v>bz</v>
       </c>
       <c r="B113" s="8">
         <v>0</v>
@@ -4866,9 +5045,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="str">
-        <v>ϴ a</v>
+        <v>ϴ b</v>
       </c>
       <c r="B114" s="8">
         <v>0</v>
@@ -4889,2418 +5068,5558 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C117" s="18" t="s">
+      <c r="C117" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D117" s="18" t="s">
+      <c r="D117" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E117" s="18" t="s">
+      <c r="E117" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F117" s="18" t="s">
+      <c r="F117" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G117" s="18" t="s">
+      <c r="G117" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H117" s="18" t="s">
+      <c r="H117" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I117" s="18" t="s">
+      <c r="I117" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="J117" s="18" t="s">
+      <c r="J117" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="K117" s="18" t="s">
+      <c r="K117" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="L117" s="18" t="s">
+      <c r="L117" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="M117" s="18" t="s">
+      <c r="M117" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N117" s="18" t="s">
+      <c r="N117" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="O117" s="18" t="s">
+      <c r="O117" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="P117" s="18" t="s">
+      <c r="P117" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="Q117" s="18" t="s">
+      <c r="Q117" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="R117" s="18" t="s">
+      <c r="R117" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="S117" s="18" t="s">
+      <c r="S117" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="T117" s="18" t="s">
+      <c r="T117" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="U117" s="18" t="s">
+      <c r="U117" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="V117" s="18" t="s">
+      <c r="V117" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="W117" s="18" t="s">
+      <c r="W117" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="X117" s="18" t="s">
+      <c r="X117" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="Y117" s="18" t="s">
+      <c r="Y117" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="Z117" s="18" t="s">
+      <c r="Z117" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="AA117" s="18" t="s">
+      <c r="AA117" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="AB117" s="18" t="s">
+      <c r="AB117" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A118" s="18" t="str">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A118" s="13" t="str">
         <f t="array" ref="A118:A144">TRANSPOSE(B117:AB117)</f>
         <v>1x</v>
       </c>
       <c r="B118" s="1">
-        <f t="array" ref="B118:D120">B109:D111</f>
+        <v>0</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0</v>
+      </c>
+      <c r="D118" s="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1">
+        <v>0</v>
+      </c>
+      <c r="F118" s="1">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1">
+        <v>0</v>
+      </c>
+      <c r="J118" s="1">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1">
+        <v>0</v>
+      </c>
+      <c r="L118" s="1">
+        <v>0</v>
+      </c>
+      <c r="M118" s="1">
+        <v>0</v>
+      </c>
+      <c r="N118" s="1">
+        <v>0</v>
+      </c>
+      <c r="O118" s="1">
+        <v>0</v>
+      </c>
+      <c r="P118" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>0</v>
+      </c>
+      <c r="R118" s="1">
+        <v>0</v>
+      </c>
+      <c r="S118" s="1">
+        <v>0</v>
+      </c>
+      <c r="T118" s="1">
+        <v>0</v>
+      </c>
+      <c r="U118" s="1">
+        <v>0</v>
+      </c>
+      <c r="V118" s="1">
+        <v>0</v>
+      </c>
+      <c r="W118" s="1">
+        <v>0</v>
+      </c>
+      <c r="X118" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A119" s="13" t="str">
+        <v>1z</v>
+      </c>
+      <c r="B119" s="1">
+        <v>0</v>
+      </c>
+      <c r="C119" s="1">
+        <v>0</v>
+      </c>
+      <c r="D119" s="1">
+        <v>0</v>
+      </c>
+      <c r="E119" s="1">
+        <v>0</v>
+      </c>
+      <c r="F119" s="1">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1">
+        <v>0</v>
+      </c>
+      <c r="J119" s="1">
+        <v>0</v>
+      </c>
+      <c r="K119" s="1">
+        <v>0</v>
+      </c>
+      <c r="L119" s="1">
+        <v>0</v>
+      </c>
+      <c r="M119" s="1">
+        <v>0</v>
+      </c>
+      <c r="N119" s="1">
+        <v>0</v>
+      </c>
+      <c r="O119" s="1">
+        <v>0</v>
+      </c>
+      <c r="P119" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="1">
+        <v>0</v>
+      </c>
+      <c r="R119" s="1">
+        <v>0</v>
+      </c>
+      <c r="S119" s="1">
+        <v>0</v>
+      </c>
+      <c r="T119" s="1">
+        <v>0</v>
+      </c>
+      <c r="U119" s="1">
+        <v>0</v>
+      </c>
+      <c r="V119" s="1">
+        <v>0</v>
+      </c>
+      <c r="W119" s="1">
+        <v>0</v>
+      </c>
+      <c r="X119" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A120" s="13" t="str">
+        <v>ϴ 1</v>
+      </c>
+      <c r="B120" s="1">
+        <v>0</v>
+      </c>
+      <c r="C120" s="1">
+        <v>0</v>
+      </c>
+      <c r="D120" s="1">
+        <v>0</v>
+      </c>
+      <c r="E120" s="1">
+        <v>0</v>
+      </c>
+      <c r="F120" s="1">
+        <v>0</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+      <c r="H120" s="1">
+        <v>0</v>
+      </c>
+      <c r="I120" s="1">
+        <v>0</v>
+      </c>
+      <c r="J120" s="1">
+        <v>0</v>
+      </c>
+      <c r="K120" s="1">
+        <v>0</v>
+      </c>
+      <c r="L120" s="1">
+        <v>0</v>
+      </c>
+      <c r="M120" s="1">
+        <v>0</v>
+      </c>
+      <c r="N120" s="1">
+        <v>0</v>
+      </c>
+      <c r="O120" s="1">
+        <v>0</v>
+      </c>
+      <c r="P120" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="1">
+        <v>0</v>
+      </c>
+      <c r="R120" s="1">
+        <v>0</v>
+      </c>
+      <c r="S120" s="1">
+        <v>0</v>
+      </c>
+      <c r="T120" s="1">
+        <v>0</v>
+      </c>
+      <c r="U120" s="1">
+        <v>0</v>
+      </c>
+      <c r="V120" s="1">
+        <v>0</v>
+      </c>
+      <c r="W120" s="1">
+        <v>0</v>
+      </c>
+      <c r="X120" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y120" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A121" s="13" t="str">
+        <v>2x</v>
+      </c>
+      <c r="B121" s="1">
+        <v>0</v>
+      </c>
+      <c r="C121" s="1">
+        <v>0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>0</v>
+      </c>
+      <c r="E121" s="1">
+        <f t="array" ref="E121:G123">B109:D111</f>
         <v>1335.5700004117459</v>
       </c>
-      <c r="C118" s="1">
+      <c r="F121" s="1">
         <v>2.0862461910941136E-11</v>
       </c>
-      <c r="D118" s="1">
+      <c r="G121" s="1">
         <v>267114.00008234923</v>
       </c>
-      <c r="E118" s="1">
-        <v>0</v>
-      </c>
-      <c r="F118" s="1">
-        <v>0</v>
-      </c>
-      <c r="G118" s="1">
-        <v>0</v>
-      </c>
-      <c r="H118" s="1">
-        <v>0</v>
-      </c>
-      <c r="I118" s="1">
-        <v>0</v>
-      </c>
-      <c r="J118" s="1">
-        <v>0</v>
-      </c>
-      <c r="K118" s="1">
-        <v>0</v>
-      </c>
-      <c r="L118" s="1">
-        <v>0</v>
-      </c>
-      <c r="M118" s="1">
-        <v>0</v>
-      </c>
-      <c r="N118" s="1">
-        <v>0</v>
-      </c>
-      <c r="O118" s="1">
-        <v>0</v>
-      </c>
-      <c r="P118" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="1">
-        <v>0</v>
-      </c>
-      <c r="R118" s="1">
-        <v>0</v>
-      </c>
-      <c r="S118" s="1">
-        <v>0</v>
-      </c>
-      <c r="T118" s="1">
-        <v>0</v>
-      </c>
-      <c r="U118" s="1">
-        <v>0</v>
-      </c>
-      <c r="V118" s="1">
-        <v>0</v>
-      </c>
-      <c r="W118" s="1">
-        <v>0</v>
-      </c>
-      <c r="X118" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y118" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z118" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA118" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB118" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A119" s="18" t="str">
+      <c r="H121" s="1">
+        <v>0</v>
+      </c>
+      <c r="I121" s="1">
+        <v>0</v>
+      </c>
+      <c r="J121" s="1">
+        <v>0</v>
+      </c>
+      <c r="K121" s="1">
+        <v>0</v>
+      </c>
+      <c r="L121" s="1">
+        <v>0</v>
+      </c>
+      <c r="M121" s="1">
+        <v>0</v>
+      </c>
+      <c r="N121" s="1">
+        <v>0</v>
+      </c>
+      <c r="O121" s="1">
+        <v>0</v>
+      </c>
+      <c r="P121" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="1">
+        <v>0</v>
+      </c>
+      <c r="R121" s="1">
+        <v>0</v>
+      </c>
+      <c r="S121" s="1">
+        <v>0</v>
+      </c>
+      <c r="T121" s="1">
+        <v>0</v>
+      </c>
+      <c r="U121" s="1">
+        <v>0</v>
+      </c>
+      <c r="V121" s="1">
+        <v>0</v>
+      </c>
+      <c r="W121" s="1">
+        <v>0</v>
+      </c>
+      <c r="X121" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB121" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A122" s="13" t="str">
+        <v>2z</v>
+      </c>
+      <c r="B122" s="1">
+        <v>0</v>
+      </c>
+      <c r="C122" s="1">
+        <v>0</v>
+      </c>
+      <c r="D122" s="1">
+        <v>0</v>
+      </c>
+      <c r="E122" s="1">
+        <v>2.0862461910941136E-11</v>
+      </c>
+      <c r="F122" s="1">
+        <v>341905.92010540701</v>
+      </c>
+      <c r="G122" s="1">
+        <v>-1.6362715224267559E-11</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
+      <c r="I122" s="1">
+        <v>0</v>
+      </c>
+      <c r="J122" s="1">
+        <v>0</v>
+      </c>
+      <c r="K122" s="1">
+        <v>0</v>
+      </c>
+      <c r="L122" s="1">
+        <v>0</v>
+      </c>
+      <c r="M122" s="1">
+        <v>0</v>
+      </c>
+      <c r="N122" s="1">
+        <v>0</v>
+      </c>
+      <c r="O122" s="1">
+        <v>0</v>
+      </c>
+      <c r="P122" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>0</v>
+      </c>
+      <c r="R122" s="1">
+        <v>0</v>
+      </c>
+      <c r="S122" s="1">
+        <v>0</v>
+      </c>
+      <c r="T122" s="1">
+        <v>0</v>
+      </c>
+      <c r="U122" s="1">
+        <v>0</v>
+      </c>
+      <c r="V122" s="1">
+        <v>0</v>
+      </c>
+      <c r="W122" s="1">
+        <v>0</v>
+      </c>
+      <c r="X122" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y122" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A123" s="13" t="str">
+        <v>ϴ 2</v>
+      </c>
+      <c r="B123" s="1">
+        <v>0</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0</v>
+      </c>
+      <c r="D123" s="1">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1">
+        <v>267114.00008234923</v>
+      </c>
+      <c r="F123" s="1">
+        <v>-1.6362715224267559E-11</v>
+      </c>
+      <c r="G123" s="1">
+        <v>71230400.021959797</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+      <c r="I123" s="1">
+        <v>0</v>
+      </c>
+      <c r="J123" s="1">
+        <v>0</v>
+      </c>
+      <c r="K123" s="1">
+        <v>0</v>
+      </c>
+      <c r="L123" s="1">
+        <v>0</v>
+      </c>
+      <c r="M123" s="1">
+        <v>0</v>
+      </c>
+      <c r="N123" s="1">
+        <v>0</v>
+      </c>
+      <c r="O123" s="1">
+        <v>0</v>
+      </c>
+      <c r="P123" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="1">
+        <v>0</v>
+      </c>
+      <c r="R123" s="1">
+        <v>0</v>
+      </c>
+      <c r="S123" s="1">
+        <v>0</v>
+      </c>
+      <c r="T123" s="1">
+        <v>0</v>
+      </c>
+      <c r="U123" s="1">
+        <v>0</v>
+      </c>
+      <c r="V123" s="1">
+        <v>0</v>
+      </c>
+      <c r="W123" s="1">
+        <v>0</v>
+      </c>
+      <c r="X123" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y123" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A124" s="13" t="str">
+        <v>3x</v>
+      </c>
+      <c r="B124" s="1">
+        <v>0</v>
+      </c>
+      <c r="C124" s="1">
+        <v>0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>0</v>
+      </c>
+      <c r="E124" s="1">
+        <v>0</v>
+      </c>
+      <c r="F124" s="1">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="1">
+        <v>0</v>
+      </c>
+      <c r="J124" s="1">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1">
+        <v>0</v>
+      </c>
+      <c r="L124" s="1">
+        <v>0</v>
+      </c>
+      <c r="M124" s="1">
+        <v>0</v>
+      </c>
+      <c r="N124" s="1">
+        <v>0</v>
+      </c>
+      <c r="O124" s="1">
+        <v>0</v>
+      </c>
+      <c r="P124" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="1">
+        <v>0</v>
+      </c>
+      <c r="R124" s="1">
+        <v>0</v>
+      </c>
+      <c r="S124" s="1">
+        <v>0</v>
+      </c>
+      <c r="T124" s="1">
+        <v>0</v>
+      </c>
+      <c r="U124" s="1">
+        <v>0</v>
+      </c>
+      <c r="V124" s="1">
+        <v>0</v>
+      </c>
+      <c r="W124" s="1">
+        <v>0</v>
+      </c>
+      <c r="X124" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y124" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z124" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA124" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A125" s="13" t="str">
+        <v>3z</v>
+      </c>
+      <c r="B125" s="1">
+        <v>0</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0</v>
+      </c>
+      <c r="D125" s="1">
+        <v>0</v>
+      </c>
+      <c r="E125" s="1">
+        <v>0</v>
+      </c>
+      <c r="F125" s="1">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+      <c r="I125" s="1">
+        <v>0</v>
+      </c>
+      <c r="J125" s="1">
+        <v>0</v>
+      </c>
+      <c r="K125" s="1">
+        <v>0</v>
+      </c>
+      <c r="L125" s="1">
+        <v>0</v>
+      </c>
+      <c r="M125" s="1">
+        <v>0</v>
+      </c>
+      <c r="N125" s="1">
+        <v>0</v>
+      </c>
+      <c r="O125" s="1">
+        <v>0</v>
+      </c>
+      <c r="P125" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="1">
+        <v>0</v>
+      </c>
+      <c r="R125" s="1">
+        <v>0</v>
+      </c>
+      <c r="S125" s="1">
+        <v>0</v>
+      </c>
+      <c r="T125" s="1">
+        <v>0</v>
+      </c>
+      <c r="U125" s="1">
+        <v>0</v>
+      </c>
+      <c r="V125" s="1">
+        <v>0</v>
+      </c>
+      <c r="W125" s="1">
+        <v>0</v>
+      </c>
+      <c r="X125" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y125" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z125" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A126" s="13" t="str">
+        <v>ϴ 3</v>
+      </c>
+      <c r="B126" s="1">
+        <v>0</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>0</v>
+      </c>
+      <c r="E126" s="1">
+        <v>0</v>
+      </c>
+      <c r="F126" s="1">
+        <v>0</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+      <c r="I126" s="1">
+        <v>0</v>
+      </c>
+      <c r="J126" s="1">
+        <v>0</v>
+      </c>
+      <c r="K126" s="1">
+        <v>0</v>
+      </c>
+      <c r="L126" s="1">
+        <v>0</v>
+      </c>
+      <c r="M126" s="1">
+        <v>0</v>
+      </c>
+      <c r="N126" s="1">
+        <v>0</v>
+      </c>
+      <c r="O126" s="1">
+        <v>0</v>
+      </c>
+      <c r="P126" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="1">
+        <v>0</v>
+      </c>
+      <c r="R126" s="1">
+        <v>0</v>
+      </c>
+      <c r="S126" s="1">
+        <v>0</v>
+      </c>
+      <c r="T126" s="1">
+        <v>0</v>
+      </c>
+      <c r="U126" s="1">
+        <v>0</v>
+      </c>
+      <c r="V126" s="1">
+        <v>0</v>
+      </c>
+      <c r="W126" s="1">
+        <v>0</v>
+      </c>
+      <c r="X126" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A127" s="13" t="str">
+        <v>4x</v>
+      </c>
+      <c r="B127" s="1">
+        <v>0</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0</v>
+      </c>
+      <c r="D127" s="1">
+        <v>0</v>
+      </c>
+      <c r="E127" s="1">
+        <v>0</v>
+      </c>
+      <c r="F127" s="1">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+      <c r="I127" s="1">
+        <v>0</v>
+      </c>
+      <c r="J127" s="1">
+        <v>0</v>
+      </c>
+      <c r="K127" s="1">
+        <v>0</v>
+      </c>
+      <c r="L127" s="1">
+        <v>0</v>
+      </c>
+      <c r="M127" s="1">
+        <v>0</v>
+      </c>
+      <c r="N127" s="1">
+        <v>0</v>
+      </c>
+      <c r="O127" s="1">
+        <v>0</v>
+      </c>
+      <c r="P127" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="1">
+        <v>0</v>
+      </c>
+      <c r="R127" s="1">
+        <v>0</v>
+      </c>
+      <c r="S127" s="1">
+        <v>0</v>
+      </c>
+      <c r="T127" s="1">
+        <v>0</v>
+      </c>
+      <c r="U127" s="1">
+        <v>0</v>
+      </c>
+      <c r="V127" s="1">
+        <v>0</v>
+      </c>
+      <c r="W127" s="1">
+        <v>0</v>
+      </c>
+      <c r="X127" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y127" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z127" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA127" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A128" s="13" t="str">
+        <v>4z</v>
+      </c>
+      <c r="B128" s="1">
+        <v>0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>0</v>
+      </c>
+      <c r="D128" s="1">
+        <v>0</v>
+      </c>
+      <c r="E128" s="1">
+        <v>0</v>
+      </c>
+      <c r="F128" s="1">
+        <v>0</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+      <c r="I128" s="1">
+        <v>0</v>
+      </c>
+      <c r="J128" s="1">
+        <v>0</v>
+      </c>
+      <c r="K128" s="1">
+        <v>0</v>
+      </c>
+      <c r="L128" s="1">
+        <v>0</v>
+      </c>
+      <c r="M128" s="1">
+        <v>0</v>
+      </c>
+      <c r="N128" s="1">
+        <v>0</v>
+      </c>
+      <c r="O128" s="1">
+        <v>0</v>
+      </c>
+      <c r="P128" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="1">
+        <v>0</v>
+      </c>
+      <c r="R128" s="1">
+        <v>0</v>
+      </c>
+      <c r="S128" s="1">
+        <v>0</v>
+      </c>
+      <c r="T128" s="1">
+        <v>0</v>
+      </c>
+      <c r="U128" s="1">
+        <v>0</v>
+      </c>
+      <c r="V128" s="1">
+        <v>0</v>
+      </c>
+      <c r="W128" s="1">
+        <v>0</v>
+      </c>
+      <c r="X128" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y128" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A129" s="13" t="str">
+        <v>ϴ 4</v>
+      </c>
+      <c r="B129" s="1">
+        <v>0</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0</v>
+      </c>
+      <c r="D129" s="1">
+        <v>0</v>
+      </c>
+      <c r="E129" s="1">
+        <v>0</v>
+      </c>
+      <c r="F129" s="1">
+        <v>0</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+      <c r="I129" s="1">
+        <v>0</v>
+      </c>
+      <c r="J129" s="1">
+        <v>0</v>
+      </c>
+      <c r="K129" s="1">
+        <v>0</v>
+      </c>
+      <c r="L129" s="1">
+        <v>0</v>
+      </c>
+      <c r="M129" s="1">
+        <v>0</v>
+      </c>
+      <c r="N129" s="1">
+        <v>0</v>
+      </c>
+      <c r="O129" s="1">
+        <v>0</v>
+      </c>
+      <c r="P129" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="1">
+        <v>0</v>
+      </c>
+      <c r="R129" s="1">
+        <v>0</v>
+      </c>
+      <c r="S129" s="1">
+        <v>0</v>
+      </c>
+      <c r="T129" s="1">
+        <v>0</v>
+      </c>
+      <c r="U129" s="1">
+        <v>0</v>
+      </c>
+      <c r="V129" s="1">
+        <v>0</v>
+      </c>
+      <c r="W129" s="1">
+        <v>0</v>
+      </c>
+      <c r="X129" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y129" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA129" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A130" s="13" t="str">
+        <v>5x</v>
+      </c>
+      <c r="B130" s="1">
+        <v>0</v>
+      </c>
+      <c r="C130" s="1">
+        <v>0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>0</v>
+      </c>
+      <c r="E130" s="1">
+        <v>0</v>
+      </c>
+      <c r="F130" s="1">
+        <v>0</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+      <c r="I130" s="1">
+        <v>0</v>
+      </c>
+      <c r="J130" s="1">
+        <v>0</v>
+      </c>
+      <c r="K130" s="1">
+        <v>0</v>
+      </c>
+      <c r="L130" s="1">
+        <v>0</v>
+      </c>
+      <c r="M130" s="1">
+        <v>0</v>
+      </c>
+      <c r="N130" s="1">
+        <v>0</v>
+      </c>
+      <c r="O130" s="1">
+        <v>0</v>
+      </c>
+      <c r="P130" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="1">
+        <v>0</v>
+      </c>
+      <c r="R130" s="1">
+        <v>0</v>
+      </c>
+      <c r="S130" s="1">
+        <v>0</v>
+      </c>
+      <c r="T130" s="1">
+        <v>0</v>
+      </c>
+      <c r="U130" s="1">
+        <v>0</v>
+      </c>
+      <c r="V130" s="1">
+        <v>0</v>
+      </c>
+      <c r="W130" s="1">
+        <v>0</v>
+      </c>
+      <c r="X130" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A131" s="13" t="str">
+        <v>5z</v>
+      </c>
+      <c r="B131" s="1">
+        <v>0</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0</v>
+      </c>
+      <c r="D131" s="1">
+        <v>0</v>
+      </c>
+      <c r="E131" s="1">
+        <v>0</v>
+      </c>
+      <c r="F131" s="1">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1">
+        <v>0</v>
+      </c>
+      <c r="J131" s="1">
+        <v>0</v>
+      </c>
+      <c r="K131" s="1">
+        <v>0</v>
+      </c>
+      <c r="L131" s="1">
+        <v>0</v>
+      </c>
+      <c r="M131" s="1">
+        <v>0</v>
+      </c>
+      <c r="N131" s="1">
+        <v>0</v>
+      </c>
+      <c r="O131" s="1">
+        <v>0</v>
+      </c>
+      <c r="P131" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="1">
+        <v>0</v>
+      </c>
+      <c r="R131" s="1">
+        <v>0</v>
+      </c>
+      <c r="S131" s="1">
+        <v>0</v>
+      </c>
+      <c r="T131" s="1">
+        <v>0</v>
+      </c>
+      <c r="U131" s="1">
+        <v>0</v>
+      </c>
+      <c r="V131" s="1">
+        <v>0</v>
+      </c>
+      <c r="W131" s="1">
+        <v>0</v>
+      </c>
+      <c r="X131" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A132" s="13" t="str">
+        <v>ϴ 5</v>
+      </c>
+      <c r="B132" s="1">
+        <v>0</v>
+      </c>
+      <c r="C132" s="1">
+        <v>0</v>
+      </c>
+      <c r="D132" s="1">
+        <v>0</v>
+      </c>
+      <c r="E132" s="1">
+        <v>0</v>
+      </c>
+      <c r="F132" s="1">
+        <v>0</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
+      <c r="I132" s="1">
+        <v>0</v>
+      </c>
+      <c r="J132" s="1">
+        <v>0</v>
+      </c>
+      <c r="K132" s="1">
+        <v>0</v>
+      </c>
+      <c r="L132" s="1">
+        <v>0</v>
+      </c>
+      <c r="M132" s="1">
+        <v>0</v>
+      </c>
+      <c r="N132" s="1">
+        <v>0</v>
+      </c>
+      <c r="O132" s="1">
+        <v>0</v>
+      </c>
+      <c r="P132" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="1">
+        <v>0</v>
+      </c>
+      <c r="R132" s="1">
+        <v>0</v>
+      </c>
+      <c r="S132" s="1">
+        <v>0</v>
+      </c>
+      <c r="T132" s="1">
+        <v>0</v>
+      </c>
+      <c r="U132" s="1">
+        <v>0</v>
+      </c>
+      <c r="V132" s="1">
+        <v>0</v>
+      </c>
+      <c r="W132" s="1">
+        <v>0</v>
+      </c>
+      <c r="X132" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A133" s="13" t="str">
+        <v>6x</v>
+      </c>
+      <c r="B133" s="1">
+        <v>0</v>
+      </c>
+      <c r="C133" s="1">
+        <v>0</v>
+      </c>
+      <c r="D133" s="1">
+        <v>0</v>
+      </c>
+      <c r="E133" s="1">
+        <v>0</v>
+      </c>
+      <c r="F133" s="1">
+        <v>0</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+      <c r="I133" s="1">
+        <v>0</v>
+      </c>
+      <c r="J133" s="1">
+        <v>0</v>
+      </c>
+      <c r="K133" s="1">
+        <v>0</v>
+      </c>
+      <c r="L133" s="1">
+        <v>0</v>
+      </c>
+      <c r="M133" s="1">
+        <v>0</v>
+      </c>
+      <c r="N133" s="1">
+        <v>0</v>
+      </c>
+      <c r="O133" s="1">
+        <v>0</v>
+      </c>
+      <c r="P133" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="1">
+        <v>0</v>
+      </c>
+      <c r="R133" s="1">
+        <v>0</v>
+      </c>
+      <c r="S133" s="1">
+        <v>0</v>
+      </c>
+      <c r="T133" s="1">
+        <v>0</v>
+      </c>
+      <c r="U133" s="1">
+        <v>0</v>
+      </c>
+      <c r="V133" s="1">
+        <v>0</v>
+      </c>
+      <c r="W133" s="1">
+        <v>0</v>
+      </c>
+      <c r="X133" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y133" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A134" s="13" t="str">
+        <v>6z</v>
+      </c>
+      <c r="B134" s="1">
+        <v>0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>0</v>
+      </c>
+      <c r="D134" s="1">
+        <v>0</v>
+      </c>
+      <c r="E134" s="1">
+        <v>0</v>
+      </c>
+      <c r="F134" s="1">
+        <v>0</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+      <c r="I134" s="1">
+        <v>0</v>
+      </c>
+      <c r="J134" s="1">
+        <v>0</v>
+      </c>
+      <c r="K134" s="1">
+        <v>0</v>
+      </c>
+      <c r="L134" s="1">
+        <v>0</v>
+      </c>
+      <c r="M134" s="1">
+        <v>0</v>
+      </c>
+      <c r="N134" s="1">
+        <v>0</v>
+      </c>
+      <c r="O134" s="1">
+        <v>0</v>
+      </c>
+      <c r="P134" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="1">
+        <v>0</v>
+      </c>
+      <c r="R134" s="1">
+        <v>0</v>
+      </c>
+      <c r="S134" s="1">
+        <v>0</v>
+      </c>
+      <c r="T134" s="1">
+        <v>0</v>
+      </c>
+      <c r="U134" s="1">
+        <v>0</v>
+      </c>
+      <c r="V134" s="1">
+        <v>0</v>
+      </c>
+      <c r="W134" s="1">
+        <v>0</v>
+      </c>
+      <c r="X134" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y134" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A135" s="13" t="str">
+        <v>ϴ 6</v>
+      </c>
+      <c r="B135" s="1">
+        <v>0</v>
+      </c>
+      <c r="C135" s="1">
+        <v>0</v>
+      </c>
+      <c r="D135" s="1">
+        <v>0</v>
+      </c>
+      <c r="E135" s="1">
+        <v>0</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+      <c r="I135" s="1">
+        <v>0</v>
+      </c>
+      <c r="J135" s="1">
+        <v>0</v>
+      </c>
+      <c r="K135" s="1">
+        <v>0</v>
+      </c>
+      <c r="L135" s="1">
+        <v>0</v>
+      </c>
+      <c r="M135" s="1">
+        <v>0</v>
+      </c>
+      <c r="N135" s="1">
+        <v>0</v>
+      </c>
+      <c r="O135" s="1">
+        <v>0</v>
+      </c>
+      <c r="P135" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="1">
+        <v>0</v>
+      </c>
+      <c r="R135" s="1">
+        <v>0</v>
+      </c>
+      <c r="S135" s="1">
+        <v>0</v>
+      </c>
+      <c r="T135" s="1">
+        <v>0</v>
+      </c>
+      <c r="U135" s="1">
+        <v>0</v>
+      </c>
+      <c r="V135" s="1">
+        <v>0</v>
+      </c>
+      <c r="W135" s="1">
+        <v>0</v>
+      </c>
+      <c r="X135" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y135" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A136" s="13" t="str">
+        <v>ax</v>
+      </c>
+      <c r="B136" s="1">
+        <v>0</v>
+      </c>
+      <c r="C136" s="1">
+        <v>0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>0</v>
+      </c>
+      <c r="E136" s="1">
+        <v>0</v>
+      </c>
+      <c r="F136" s="1">
+        <v>0</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
+      </c>
+      <c r="I136" s="1">
+        <v>0</v>
+      </c>
+      <c r="J136" s="1">
+        <v>0</v>
+      </c>
+      <c r="K136" s="1">
+        <v>0</v>
+      </c>
+      <c r="L136" s="1">
+        <v>0</v>
+      </c>
+      <c r="M136" s="1">
+        <v>0</v>
+      </c>
+      <c r="N136" s="1">
+        <v>0</v>
+      </c>
+      <c r="O136" s="1">
+        <v>0</v>
+      </c>
+      <c r="P136" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="1">
+        <v>0</v>
+      </c>
+      <c r="R136" s="1">
+        <v>0</v>
+      </c>
+      <c r="S136" s="1">
+        <v>0</v>
+      </c>
+      <c r="T136" s="1">
+        <v>0</v>
+      </c>
+      <c r="U136" s="1">
+        <v>0</v>
+      </c>
+      <c r="V136" s="1">
+        <v>0</v>
+      </c>
+      <c r="W136" s="1">
+        <v>0</v>
+      </c>
+      <c r="X136" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A137" s="13" t="str">
+        <v>az</v>
+      </c>
+      <c r="B137" s="1">
+        <v>0</v>
+      </c>
+      <c r="C137" s="1">
+        <v>0</v>
+      </c>
+      <c r="D137" s="1">
+        <v>0</v>
+      </c>
+      <c r="E137" s="1">
+        <v>0</v>
+      </c>
+      <c r="F137" s="1">
+        <v>0</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+      <c r="I137" s="1">
+        <v>0</v>
+      </c>
+      <c r="J137" s="1">
+        <v>0</v>
+      </c>
+      <c r="K137" s="1">
+        <v>0</v>
+      </c>
+      <c r="L137" s="1">
+        <v>0</v>
+      </c>
+      <c r="M137" s="1">
+        <v>0</v>
+      </c>
+      <c r="N137" s="1">
+        <v>0</v>
+      </c>
+      <c r="O137" s="1">
+        <v>0</v>
+      </c>
+      <c r="P137" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="1">
+        <v>0</v>
+      </c>
+      <c r="R137" s="1">
+        <v>0</v>
+      </c>
+      <c r="S137" s="1">
+        <v>0</v>
+      </c>
+      <c r="T137" s="1">
+        <v>0</v>
+      </c>
+      <c r="U137" s="1">
+        <v>0</v>
+      </c>
+      <c r="V137" s="1">
+        <v>0</v>
+      </c>
+      <c r="W137" s="1">
+        <v>0</v>
+      </c>
+      <c r="X137" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A138" s="13" t="str">
+        <v>ϴ a</v>
+      </c>
+      <c r="B138" s="1">
+        <v>0</v>
+      </c>
+      <c r="C138" s="1">
+        <v>0</v>
+      </c>
+      <c r="D138" s="1">
+        <v>0</v>
+      </c>
+      <c r="E138" s="1">
+        <v>0</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0</v>
+      </c>
+      <c r="I138" s="1">
+        <v>0</v>
+      </c>
+      <c r="J138" s="1">
+        <v>0</v>
+      </c>
+      <c r="K138" s="1">
+        <v>0</v>
+      </c>
+      <c r="L138" s="1">
+        <v>0</v>
+      </c>
+      <c r="M138" s="1">
+        <v>0</v>
+      </c>
+      <c r="N138" s="1">
+        <v>0</v>
+      </c>
+      <c r="O138" s="1">
+        <v>0</v>
+      </c>
+      <c r="P138" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="1">
+        <v>0</v>
+      </c>
+      <c r="R138" s="1">
+        <v>0</v>
+      </c>
+      <c r="S138" s="1">
+        <v>0</v>
+      </c>
+      <c r="T138" s="1">
+        <v>0</v>
+      </c>
+      <c r="U138" s="1">
+        <v>0</v>
+      </c>
+      <c r="V138" s="1">
+        <v>0</v>
+      </c>
+      <c r="W138" s="1">
+        <v>0</v>
+      </c>
+      <c r="X138" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A139" s="13" t="str">
+        <v>bx</v>
+      </c>
+      <c r="B139" s="1">
+        <v>0</v>
+      </c>
+      <c r="C139" s="1">
+        <v>0</v>
+      </c>
+      <c r="D139" s="1">
+        <v>0</v>
+      </c>
+      <c r="E139" s="1">
+        <v>0</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+      <c r="I139" s="1">
+        <v>0</v>
+      </c>
+      <c r="J139" s="1">
+        <v>0</v>
+      </c>
+      <c r="K139" s="1">
+        <v>0</v>
+      </c>
+      <c r="L139" s="1">
+        <v>0</v>
+      </c>
+      <c r="M139" s="1">
+        <v>0</v>
+      </c>
+      <c r="N139" s="1">
+        <v>0</v>
+      </c>
+      <c r="O139" s="1">
+        <v>0</v>
+      </c>
+      <c r="P139" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="1">
+        <v>0</v>
+      </c>
+      <c r="R139" s="1">
+        <v>0</v>
+      </c>
+      <c r="S139" s="1">
+        <v>0</v>
+      </c>
+      <c r="T139" s="1">
+        <v>0</v>
+      </c>
+      <c r="U139" s="1">
+        <v>0</v>
+      </c>
+      <c r="V139" s="1">
+        <v>0</v>
+      </c>
+      <c r="W139" s="1">
+        <v>0</v>
+      </c>
+      <c r="X139" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A140" s="13" t="str">
+        <v>bz</v>
+      </c>
+      <c r="B140" s="1">
+        <v>0</v>
+      </c>
+      <c r="C140" s="1">
+        <v>0</v>
+      </c>
+      <c r="D140" s="1">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1">
+        <v>0</v>
+      </c>
+      <c r="F140" s="1">
+        <v>0</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+      <c r="I140" s="1">
+        <v>0</v>
+      </c>
+      <c r="J140" s="1">
+        <v>0</v>
+      </c>
+      <c r="K140" s="1">
+        <v>0</v>
+      </c>
+      <c r="L140" s="1">
+        <v>0</v>
+      </c>
+      <c r="M140" s="1">
+        <v>0</v>
+      </c>
+      <c r="N140" s="1">
+        <v>0</v>
+      </c>
+      <c r="O140" s="1">
+        <v>0</v>
+      </c>
+      <c r="P140" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="1">
+        <v>0</v>
+      </c>
+      <c r="R140" s="1">
+        <v>0</v>
+      </c>
+      <c r="S140" s="1">
+        <v>0</v>
+      </c>
+      <c r="T140" s="1">
+        <v>0</v>
+      </c>
+      <c r="U140" s="1">
+        <v>0</v>
+      </c>
+      <c r="V140" s="1">
+        <v>0</v>
+      </c>
+      <c r="W140" s="1">
+        <v>0</v>
+      </c>
+      <c r="X140" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y140" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A141" s="13" t="str">
+        <v>ϴ b</v>
+      </c>
+      <c r="B141" s="1">
+        <v>0</v>
+      </c>
+      <c r="C141" s="1">
+        <v>0</v>
+      </c>
+      <c r="D141" s="1">
+        <v>0</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
+      </c>
+      <c r="I141" s="1">
+        <v>0</v>
+      </c>
+      <c r="J141" s="1">
+        <v>0</v>
+      </c>
+      <c r="K141" s="1">
+        <v>0</v>
+      </c>
+      <c r="L141" s="1">
+        <v>0</v>
+      </c>
+      <c r="M141" s="1">
+        <v>0</v>
+      </c>
+      <c r="N141" s="1">
+        <v>0</v>
+      </c>
+      <c r="O141" s="1">
+        <v>0</v>
+      </c>
+      <c r="P141" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="1">
+        <v>0</v>
+      </c>
+      <c r="R141" s="1">
+        <v>0</v>
+      </c>
+      <c r="S141" s="1">
+        <v>0</v>
+      </c>
+      <c r="T141" s="1">
+        <v>0</v>
+      </c>
+      <c r="U141" s="1">
+        <v>0</v>
+      </c>
+      <c r="V141" s="1">
+        <v>0</v>
+      </c>
+      <c r="W141" s="1">
+        <v>0</v>
+      </c>
+      <c r="X141" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A142" s="13" t="str">
+        <v>cx</v>
+      </c>
+      <c r="B142" s="1">
+        <v>0</v>
+      </c>
+      <c r="C142" s="1">
+        <v>0</v>
+      </c>
+      <c r="D142" s="1">
+        <v>0</v>
+      </c>
+      <c r="E142" s="1">
+        <v>0</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+      <c r="I142" s="1">
+        <v>0</v>
+      </c>
+      <c r="J142" s="1">
+        <v>0</v>
+      </c>
+      <c r="K142" s="1">
+        <v>0</v>
+      </c>
+      <c r="L142" s="1">
+        <v>0</v>
+      </c>
+      <c r="M142" s="1">
+        <v>0</v>
+      </c>
+      <c r="N142" s="1">
+        <v>0</v>
+      </c>
+      <c r="O142" s="1">
+        <v>0</v>
+      </c>
+      <c r="P142" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="1">
+        <v>0</v>
+      </c>
+      <c r="R142" s="1">
+        <v>0</v>
+      </c>
+      <c r="S142" s="1">
+        <v>0</v>
+      </c>
+      <c r="T142" s="1">
+        <v>0</v>
+      </c>
+      <c r="U142" s="1">
+        <v>0</v>
+      </c>
+      <c r="V142" s="1">
+        <v>0</v>
+      </c>
+      <c r="W142" s="1">
+        <v>0</v>
+      </c>
+      <c r="X142" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A143" s="13" t="str">
+        <v>cz</v>
+      </c>
+      <c r="B143" s="1">
+        <v>0</v>
+      </c>
+      <c r="C143" s="1">
+        <v>0</v>
+      </c>
+      <c r="D143" s="1">
+        <v>0</v>
+      </c>
+      <c r="E143" s="1">
+        <v>0</v>
+      </c>
+      <c r="F143" s="1">
+        <v>0</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0</v>
+      </c>
+      <c r="I143" s="1">
+        <v>0</v>
+      </c>
+      <c r="J143" s="1">
+        <v>0</v>
+      </c>
+      <c r="K143" s="1">
+        <v>0</v>
+      </c>
+      <c r="L143" s="1">
+        <v>0</v>
+      </c>
+      <c r="M143" s="1">
+        <v>0</v>
+      </c>
+      <c r="N143" s="1">
+        <v>0</v>
+      </c>
+      <c r="O143" s="1">
+        <v>0</v>
+      </c>
+      <c r="P143" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="1">
+        <v>0</v>
+      </c>
+      <c r="R143" s="1">
+        <v>0</v>
+      </c>
+      <c r="S143" s="1">
+        <v>0</v>
+      </c>
+      <c r="T143" s="1">
+        <v>0</v>
+      </c>
+      <c r="U143" s="1">
+        <v>0</v>
+      </c>
+      <c r="V143" s="1">
+        <v>0</v>
+      </c>
+      <c r="W143" s="1">
+        <v>0</v>
+      </c>
+      <c r="X143" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y143" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA143" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A144" s="13" t="str">
+        <v>ϴ c</v>
+      </c>
+      <c r="B144" s="1">
+        <v>0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>0</v>
+      </c>
+      <c r="D144" s="1">
+        <v>0</v>
+      </c>
+      <c r="E144" s="1">
+        <v>0</v>
+      </c>
+      <c r="F144" s="1">
+        <v>0</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>0</v>
+      </c>
+      <c r="J144" s="1">
+        <v>0</v>
+      </c>
+      <c r="K144" s="1">
+        <v>0</v>
+      </c>
+      <c r="L144" s="1">
+        <v>0</v>
+      </c>
+      <c r="M144" s="1">
+        <v>0</v>
+      </c>
+      <c r="N144" s="1">
+        <v>0</v>
+      </c>
+      <c r="O144" s="1">
+        <v>0</v>
+      </c>
+      <c r="P144" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="1">
+        <v>0</v>
+      </c>
+      <c r="R144" s="1">
+        <v>0</v>
+      </c>
+      <c r="S144" s="1">
+        <v>0</v>
+      </c>
+      <c r="T144" s="1">
+        <v>0</v>
+      </c>
+      <c r="U144" s="1">
+        <v>0</v>
+      </c>
+      <c r="V144" s="1">
+        <v>0</v>
+      </c>
+      <c r="W144" s="1">
+        <v>0</v>
+      </c>
+      <c r="X144" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA144" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B147" s="14"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="14"/>
+      <c r="E147" s="14"/>
+      <c r="F147" s="14"/>
+      <c r="G147" s="14"/>
+      <c r="H147" s="14"/>
+      <c r="I147" s="14"/>
+      <c r="J147" s="14"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" s="1">
+        <v>625</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B150" s="1">
+        <f>POWER(25,4)/12</f>
+        <v>32552.083333333332</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B151" s="1">
+        <v>400</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B152" s="1">
+        <f>15100*SQRT(210)</f>
+        <v>218819.78886746051</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B154" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B155" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" s="3">
+        <f>(B152*B149)/B151</f>
+        <v>341905.92010540701</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B156" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="3">
+        <f>(12*B152*B150)/(B151^3)</f>
+        <v>1335.5700004117459</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B157" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="3">
+        <f>(6*B152*B150)/(B151^2)</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B158" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" s="3">
+        <f>+(4*B152*B150)/(B151)</f>
+        <v>71230400.021959797</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B159" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C159" s="3">
+        <f>+(2*B152*B150)/B151</f>
+        <v>35615200.010979898</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C160" s="4"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A161" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B161" s="15"/>
+      <c r="C161" s="15"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="15"/>
+      <c r="F161" s="15"/>
+      <c r="G161" s="15"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" s="5" t="str">
+        <f t="array" ref="A163:A168">TRANSPOSE(B162:G162)</f>
+        <v>3x</v>
+      </c>
+      <c r="B163" s="6">
+        <f>+C155</f>
+        <v>341905.92010540701</v>
+      </c>
+      <c r="C163" s="6">
+        <v>0</v>
+      </c>
+      <c r="D163" s="6">
+        <v>0</v>
+      </c>
+      <c r="E163" s="7">
+        <f>+-C155</f>
+        <v>-341905.92010540701</v>
+      </c>
+      <c r="F163" s="7">
+        <v>0</v>
+      </c>
+      <c r="G163" s="7">
+        <v>0</v>
+      </c>
+      <c r="H163" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I163" s="16"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A164" s="5" t="str">
+        <v>3z</v>
+      </c>
+      <c r="B164" s="6">
+        <v>0</v>
+      </c>
+      <c r="C164" s="6">
+        <f>+C156</f>
+        <v>1335.5700004117459</v>
+      </c>
+      <c r="D164" s="6">
+        <f>+C157</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="E164" s="7">
+        <v>0</v>
+      </c>
+      <c r="F164" s="7">
+        <f>-C156</f>
+        <v>-1335.5700004117459</v>
+      </c>
+      <c r="G164" s="7">
+        <f>+C157</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="H164" s="16"/>
+      <c r="I164" s="16"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A165" s="5" t="str">
+        <v>ϴ 3</v>
+      </c>
+      <c r="B165" s="6">
+        <v>0</v>
+      </c>
+      <c r="C165" s="6">
+        <f>+C157</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="D165" s="6">
+        <f>+C158</f>
+        <v>71230400.021959797</v>
+      </c>
+      <c r="E165" s="7">
+        <v>0</v>
+      </c>
+      <c r="F165" s="7">
+        <f>+-C157</f>
+        <v>-267114.00008234923</v>
+      </c>
+      <c r="G165" s="7">
+        <f>+C159</f>
+        <v>35615200.010979898</v>
+      </c>
+      <c r="H165" s="16"/>
+      <c r="I165" s="16"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A166" s="5" t="str">
+        <v>cx</v>
+      </c>
+      <c r="B166" s="8">
+        <f>-C155</f>
+        <v>-341905.92010540701</v>
+      </c>
+      <c r="C166" s="8">
+        <v>0</v>
+      </c>
+      <c r="D166" s="8">
+        <v>0</v>
+      </c>
+      <c r="E166" s="9">
+        <f>+C155</f>
+        <v>341905.92010540701</v>
+      </c>
+      <c r="F166" s="9">
+        <v>0</v>
+      </c>
+      <c r="G166" s="9">
+        <v>0</v>
+      </c>
+      <c r="H166" s="16"/>
+      <c r="I166" s="16"/>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" s="5" t="str">
+        <v>z</v>
+      </c>
+      <c r="B167" s="8">
+        <v>0</v>
+      </c>
+      <c r="C167" s="8">
+        <f>-C156</f>
+        <v>-1335.5700004117459</v>
+      </c>
+      <c r="D167" s="8">
+        <f>-C157</f>
+        <v>-267114.00008234923</v>
+      </c>
+      <c r="E167" s="9">
+        <v>0</v>
+      </c>
+      <c r="F167" s="9">
+        <f>C156</f>
+        <v>1335.5700004117459</v>
+      </c>
+      <c r="G167" s="9">
+        <f>-C157</f>
+        <v>-267114.00008234923</v>
+      </c>
+      <c r="H167" s="16"/>
+      <c r="I167" s="16"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A168" s="5" t="str">
+        <v>ϴ c</v>
+      </c>
+      <c r="B168" s="8">
+        <v>0</v>
+      </c>
+      <c r="C168" s="8">
+        <f>+C157</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="D168" s="8">
+        <f>+C159</f>
+        <v>35615200.010979898</v>
+      </c>
+      <c r="E168" s="9">
+        <v>0</v>
+      </c>
+      <c r="F168" s="9">
+        <f>-C157</f>
+        <v>-267114.00008234923</v>
+      </c>
+      <c r="G168" s="9">
+        <f>C158</f>
+        <v>71230400.021959797</v>
+      </c>
+      <c r="H168" s="16"/>
+      <c r="I168" s="16"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B170" s="15"/>
+      <c r="C170" s="15"/>
+      <c r="D170" s="15"/>
+      <c r="E170" s="15"/>
+      <c r="F170" s="15"/>
+      <c r="G170" s="15"/>
+      <c r="H170" s="15"/>
+      <c r="I170" s="15"/>
+      <c r="J170" s="15"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" s="4"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D171" s="17"/>
+      <c r="E171" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F171" s="17"/>
+      <c r="G171" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H171" s="17"/>
+      <c r="I171" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J171" s="17"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B172" s="10">
+        <v>90</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D172" s="11">
+        <f>+B163</f>
+        <v>341905.92010540701</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F172" s="11">
+        <f>+E163</f>
+        <v>-341905.92010540701</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H172" s="11">
+        <f>+B166</f>
+        <v>-341905.92010540701</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J172" s="12">
+        <f>+E166</f>
+        <v>341905.92010540701</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B173" s="4">
+        <f>SIN(RADIANS(B172))</f>
+        <v>1</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D173" s="11">
+        <f>+C164</f>
+        <v>1335.5700004117459</v>
+      </c>
+      <c r="E173" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F173" s="11">
+        <f>+F164</f>
+        <v>-1335.5700004117459</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H173" s="11">
+        <f>+C167</f>
+        <v>-1335.5700004117459</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J173" s="12">
+        <f>+F167</f>
+        <v>1335.5700004117459</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B174" s="4">
+        <f>COS(RADIANS(B172))</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D174" s="11">
+        <f>+D165</f>
+        <v>71230400.021959797</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F174" s="11">
+        <f>+G165</f>
+        <v>35615200.010979898</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H174" s="11">
+        <f>+D168</f>
+        <v>35615200.010979898</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J174" s="12">
+        <f>+G168</f>
+        <v>71230400.021959797</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A175" s="4"/>
+      <c r="B175" s="4"/>
+      <c r="C175" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D175" s="11">
+        <f>+D164</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F175" s="11">
+        <f>+G164</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H175" s="11">
+        <f>+D167</f>
+        <v>-267114.00008234923</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J175" s="12">
+        <f>+G167</f>
+        <v>-267114.00008234923</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C176" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D176" s="11">
+        <f>+C165</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F176" s="11">
+        <f>+F165</f>
+        <v>-267114.00008234923</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H176" s="11">
+        <f>+C168</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J176" s="12">
+        <f>+F168</f>
+        <v>-267114.00008234923</v>
+      </c>
+    </row>
+    <row r="180" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B180" s="5" t="str">
+        <f t="array" ref="B180:G180">B162:G162</f>
+        <v>3x</v>
+      </c>
+      <c r="C180" s="5" t="str">
+        <v>3z</v>
+      </c>
+      <c r="D180" s="5" t="str">
+        <v>ϴ 3</v>
+      </c>
+      <c r="E180" s="5" t="str">
+        <v>cx</v>
+      </c>
+      <c r="F180" s="5" t="str">
+        <v>z</v>
+      </c>
+      <c r="G180" s="5" t="str">
+        <v>ϴ c</v>
+      </c>
+    </row>
+    <row r="181" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A181" s="5" t="str">
+        <f t="array" ref="A181:A186">+TRANSPOSE(B180:G180)</f>
+        <v>3x</v>
+      </c>
+      <c r="B181" s="6">
+        <f>(J172*B174*B174)+(J173*B173*B173)</f>
+        <v>1335.5700004117459</v>
+      </c>
+      <c r="C181" s="6">
+        <f>(J172-J173)*B174*B173</f>
+        <v>2.0862461910941136E-11</v>
+      </c>
+      <c r="D181" s="6">
+        <f>-J175*B173</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="E181" s="7">
+        <v>0</v>
+      </c>
+      <c r="F181" s="7">
+        <v>0</v>
+      </c>
+      <c r="G181" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A182" s="5" t="str">
+        <v>3z</v>
+      </c>
+      <c r="B182" s="6">
+        <f>(J172-J173)*B174*B173</f>
+        <v>2.0862461910941136E-11</v>
+      </c>
+      <c r="C182" s="6">
+        <f>+(J172*B173*B173)+(J173*B174*B174)</f>
+        <v>341905.92010540701</v>
+      </c>
+      <c r="D182" s="6">
+        <f>J175*B174</f>
+        <v>-1.6362715224267559E-11</v>
+      </c>
+      <c r="E182" s="7">
+        <v>0</v>
+      </c>
+      <c r="F182" s="7">
+        <v>0</v>
+      </c>
+      <c r="G182" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A183" s="5" t="str">
+        <v>ϴ 3</v>
+      </c>
+      <c r="B183" s="6">
+        <f>-J176*B173</f>
+        <v>267114.00008234923</v>
+      </c>
+      <c r="C183" s="6">
+        <f>J176*B174</f>
+        <v>-1.6362715224267559E-11</v>
+      </c>
+      <c r="D183" s="6">
+        <f>+J174</f>
+        <v>71230400.021959797</v>
+      </c>
+      <c r="E183" s="7">
+        <v>0</v>
+      </c>
+      <c r="F183" s="7">
+        <v>0</v>
+      </c>
+      <c r="G183" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A184" s="5" t="str">
+        <v>cx</v>
+      </c>
+      <c r="B184" s="8">
+        <v>0</v>
+      </c>
+      <c r="C184" s="8">
+        <v>0</v>
+      </c>
+      <c r="D184" s="8">
+        <v>0</v>
+      </c>
+      <c r="E184" s="9">
+        <v>0</v>
+      </c>
+      <c r="F184" s="9">
+        <v>0</v>
+      </c>
+      <c r="G184" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A185" s="5" t="str">
+        <v>z</v>
+      </c>
+      <c r="B185" s="8">
+        <v>0</v>
+      </c>
+      <c r="C185" s="8">
+        <v>0</v>
+      </c>
+      <c r="D185" s="8">
+        <v>0</v>
+      </c>
+      <c r="E185" s="9">
+        <v>0</v>
+      </c>
+      <c r="F185" s="9">
+        <v>0</v>
+      </c>
+      <c r="G185" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A186" s="5" t="str">
+        <v>ϴ c</v>
+      </c>
+      <c r="B186" s="8">
+        <v>0</v>
+      </c>
+      <c r="C186" s="8">
+        <v>0</v>
+      </c>
+      <c r="D186" s="8">
+        <v>0</v>
+      </c>
+      <c r="E186" s="9">
+        <v>0</v>
+      </c>
+      <c r="F186" s="9">
+        <v>0</v>
+      </c>
+      <c r="G186" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B189" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C189" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D189" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E189" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F189" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G189" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H189" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I189" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J189" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K189" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L189" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M189" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="N189" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="O189" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="P189" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q189" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="R189" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="S189" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="T189" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="U189" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="V189" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="W189" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="X189" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y189" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z189" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA189" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB189" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="190" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A190" s="13" t="str">
+        <f t="array" ref="A190:A216">TRANSPOSE(B189:AB189)</f>
+        <v>1x</v>
+      </c>
+      <c r="B190" s="1">
+        <v>0</v>
+      </c>
+      <c r="C190" s="1">
+        <v>0</v>
+      </c>
+      <c r="D190" s="1">
+        <v>0</v>
+      </c>
+      <c r="E190" s="1">
+        <v>0</v>
+      </c>
+      <c r="F190" s="1">
+        <v>0</v>
+      </c>
+      <c r="G190" s="1">
+        <v>0</v>
+      </c>
+      <c r="H190" s="1">
+        <v>0</v>
+      </c>
+      <c r="I190" s="1">
+        <v>0</v>
+      </c>
+      <c r="J190" s="1">
+        <v>0</v>
+      </c>
+      <c r="K190" s="1">
+        <v>0</v>
+      </c>
+      <c r="L190" s="1">
+        <v>0</v>
+      </c>
+      <c r="M190" s="1">
+        <v>0</v>
+      </c>
+      <c r="N190" s="1">
+        <v>0</v>
+      </c>
+      <c r="O190" s="1">
+        <v>0</v>
+      </c>
+      <c r="P190" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="1">
+        <v>0</v>
+      </c>
+      <c r="R190" s="1">
+        <v>0</v>
+      </c>
+      <c r="S190" s="1">
+        <v>0</v>
+      </c>
+      <c r="T190" s="1">
+        <v>0</v>
+      </c>
+      <c r="U190" s="1">
+        <v>0</v>
+      </c>
+      <c r="V190" s="1">
+        <v>0</v>
+      </c>
+      <c r="W190" s="1">
+        <v>0</v>
+      </c>
+      <c r="X190" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB190" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A191" s="13" t="str">
         <v>1z</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B191" s="1">
+        <v>0</v>
+      </c>
+      <c r="C191" s="1">
+        <v>0</v>
+      </c>
+      <c r="D191" s="1">
+        <v>0</v>
+      </c>
+      <c r="E191" s="1">
+        <v>0</v>
+      </c>
+      <c r="F191" s="1">
+        <v>0</v>
+      </c>
+      <c r="G191" s="1">
+        <v>0</v>
+      </c>
+      <c r="H191" s="1">
+        <v>0</v>
+      </c>
+      <c r="I191" s="1">
+        <v>0</v>
+      </c>
+      <c r="J191" s="1">
+        <v>0</v>
+      </c>
+      <c r="K191" s="1">
+        <v>0</v>
+      </c>
+      <c r="L191" s="1">
+        <v>0</v>
+      </c>
+      <c r="M191" s="1">
+        <v>0</v>
+      </c>
+      <c r="N191" s="1">
+        <v>0</v>
+      </c>
+      <c r="O191" s="1">
+        <v>0</v>
+      </c>
+      <c r="P191" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q191" s="1">
+        <v>0</v>
+      </c>
+      <c r="R191" s="1">
+        <v>0</v>
+      </c>
+      <c r="S191" s="1">
+        <v>0</v>
+      </c>
+      <c r="T191" s="1">
+        <v>0</v>
+      </c>
+      <c r="U191" s="1">
+        <v>0</v>
+      </c>
+      <c r="V191" s="1">
+        <v>0</v>
+      </c>
+      <c r="W191" s="1">
+        <v>0</v>
+      </c>
+      <c r="X191" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y191" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z191" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA191" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB191" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A192" s="13" t="str">
+        <v>ϴ 1</v>
+      </c>
+      <c r="B192" s="1">
+        <v>0</v>
+      </c>
+      <c r="C192" s="1">
+        <v>0</v>
+      </c>
+      <c r="D192" s="1">
+        <v>0</v>
+      </c>
+      <c r="E192" s="1">
+        <v>0</v>
+      </c>
+      <c r="F192" s="1">
+        <v>0</v>
+      </c>
+      <c r="G192" s="1">
+        <v>0</v>
+      </c>
+      <c r="H192" s="1">
+        <v>0</v>
+      </c>
+      <c r="I192" s="1">
+        <v>0</v>
+      </c>
+      <c r="J192" s="1">
+        <v>0</v>
+      </c>
+      <c r="K192" s="1">
+        <v>0</v>
+      </c>
+      <c r="L192" s="1">
+        <v>0</v>
+      </c>
+      <c r="M192" s="1">
+        <v>0</v>
+      </c>
+      <c r="N192" s="1">
+        <v>0</v>
+      </c>
+      <c r="O192" s="1">
+        <v>0</v>
+      </c>
+      <c r="P192" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q192" s="1">
+        <v>0</v>
+      </c>
+      <c r="R192" s="1">
+        <v>0</v>
+      </c>
+      <c r="S192" s="1">
+        <v>0</v>
+      </c>
+      <c r="T192" s="1">
+        <v>0</v>
+      </c>
+      <c r="U192" s="1">
+        <v>0</v>
+      </c>
+      <c r="V192" s="1">
+        <v>0</v>
+      </c>
+      <c r="W192" s="1">
+        <v>0</v>
+      </c>
+      <c r="X192" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y192" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA192" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB192" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A193" s="13" t="str">
+        <v>2x</v>
+      </c>
+      <c r="B193" s="1">
+        <v>0</v>
+      </c>
+      <c r="C193" s="1">
+        <v>0</v>
+      </c>
+      <c r="D193" s="1">
+        <v>0</v>
+      </c>
+      <c r="E193" s="1">
+        <v>0</v>
+      </c>
+      <c r="F193" s="1">
+        <v>0</v>
+      </c>
+      <c r="G193" s="1">
+        <v>0</v>
+      </c>
+      <c r="H193" s="1">
+        <v>0</v>
+      </c>
+      <c r="I193" s="1">
+        <v>0</v>
+      </c>
+      <c r="J193" s="1">
+        <v>0</v>
+      </c>
+      <c r="K193" s="1">
+        <v>0</v>
+      </c>
+      <c r="L193" s="1">
+        <v>0</v>
+      </c>
+      <c r="M193" s="1">
+        <v>0</v>
+      </c>
+      <c r="N193" s="1">
+        <v>0</v>
+      </c>
+      <c r="O193" s="1">
+        <v>0</v>
+      </c>
+      <c r="P193" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="1">
+        <v>0</v>
+      </c>
+      <c r="R193" s="1">
+        <v>0</v>
+      </c>
+      <c r="S193" s="1">
+        <v>0</v>
+      </c>
+      <c r="T193" s="1">
+        <v>0</v>
+      </c>
+      <c r="U193" s="1">
+        <v>0</v>
+      </c>
+      <c r="V193" s="1">
+        <v>0</v>
+      </c>
+      <c r="W193" s="1">
+        <v>0</v>
+      </c>
+      <c r="X193" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y193" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z193" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA193" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB193" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A194" s="13" t="str">
+        <v>2z</v>
+      </c>
+      <c r="B194" s="1">
+        <v>0</v>
+      </c>
+      <c r="C194" s="1">
+        <v>0</v>
+      </c>
+      <c r="D194" s="1">
+        <v>0</v>
+      </c>
+      <c r="E194" s="1">
+        <v>0</v>
+      </c>
+      <c r="F194" s="1">
+        <v>0</v>
+      </c>
+      <c r="G194" s="1">
+        <v>0</v>
+      </c>
+      <c r="H194" s="1">
+        <v>0</v>
+      </c>
+      <c r="I194" s="1">
+        <v>0</v>
+      </c>
+      <c r="J194" s="1">
+        <v>0</v>
+      </c>
+      <c r="K194" s="1">
+        <v>0</v>
+      </c>
+      <c r="L194" s="1">
+        <v>0</v>
+      </c>
+      <c r="M194" s="1">
+        <v>0</v>
+      </c>
+      <c r="N194" s="1">
+        <v>0</v>
+      </c>
+      <c r="O194" s="1">
+        <v>0</v>
+      </c>
+      <c r="P194" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q194" s="1">
+        <v>0</v>
+      </c>
+      <c r="R194" s="1">
+        <v>0</v>
+      </c>
+      <c r="S194" s="1">
+        <v>0</v>
+      </c>
+      <c r="T194" s="1">
+        <v>0</v>
+      </c>
+      <c r="U194" s="1">
+        <v>0</v>
+      </c>
+      <c r="V194" s="1">
+        <v>0</v>
+      </c>
+      <c r="W194" s="1">
+        <v>0</v>
+      </c>
+      <c r="X194" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y194" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB194" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A195" s="13" t="str">
+        <v>ϴ 2</v>
+      </c>
+      <c r="B195" s="1">
+        <v>0</v>
+      </c>
+      <c r="C195" s="1">
+        <v>0</v>
+      </c>
+      <c r="D195" s="1">
+        <v>0</v>
+      </c>
+      <c r="E195" s="1">
+        <v>0</v>
+      </c>
+      <c r="F195" s="1">
+        <v>0</v>
+      </c>
+      <c r="G195" s="1">
+        <v>0</v>
+      </c>
+      <c r="H195" s="1">
+        <v>0</v>
+      </c>
+      <c r="I195" s="1">
+        <v>0</v>
+      </c>
+      <c r="J195" s="1">
+        <v>0</v>
+      </c>
+      <c r="K195" s="1">
+        <v>0</v>
+      </c>
+      <c r="L195" s="1">
+        <v>0</v>
+      </c>
+      <c r="M195" s="1">
+        <v>0</v>
+      </c>
+      <c r="N195" s="1">
+        <v>0</v>
+      </c>
+      <c r="O195" s="1">
+        <v>0</v>
+      </c>
+      <c r="P195" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q195" s="1">
+        <v>0</v>
+      </c>
+      <c r="R195" s="1">
+        <v>0</v>
+      </c>
+      <c r="S195" s="1">
+        <v>0</v>
+      </c>
+      <c r="T195" s="1">
+        <v>0</v>
+      </c>
+      <c r="U195" s="1">
+        <v>0</v>
+      </c>
+      <c r="V195" s="1">
+        <v>0</v>
+      </c>
+      <c r="W195" s="1">
+        <v>0</v>
+      </c>
+      <c r="X195" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A196" s="13" t="str">
+        <v>3x</v>
+      </c>
+      <c r="B196" s="1">
+        <v>0</v>
+      </c>
+      <c r="C196" s="1">
+        <v>0</v>
+      </c>
+      <c r="D196" s="1">
+        <v>0</v>
+      </c>
+      <c r="E196" s="1">
+        <v>0</v>
+      </c>
+      <c r="F196" s="1">
+        <v>0</v>
+      </c>
+      <c r="G196" s="1">
+        <v>0</v>
+      </c>
+      <c r="H196" s="1">
+        <f t="array" ref="H196:J198">B181:D183</f>
+        <v>1335.5700004117459</v>
+      </c>
+      <c r="I196" s="1">
         <v>2.0862461910941136E-11</v>
       </c>
-      <c r="C119" s="1">
+      <c r="J196" s="1">
+        <v>267114.00008234923</v>
+      </c>
+      <c r="K196" s="1">
+        <v>0</v>
+      </c>
+      <c r="L196" s="1">
+        <v>0</v>
+      </c>
+      <c r="M196" s="1">
+        <v>0</v>
+      </c>
+      <c r="N196" s="1">
+        <v>0</v>
+      </c>
+      <c r="O196" s="1">
+        <v>0</v>
+      </c>
+      <c r="P196" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q196" s="1">
+        <v>0</v>
+      </c>
+      <c r="R196" s="1">
+        <v>0</v>
+      </c>
+      <c r="S196" s="1">
+        <v>0</v>
+      </c>
+      <c r="T196" s="1">
+        <v>0</v>
+      </c>
+      <c r="U196" s="1">
+        <v>0</v>
+      </c>
+      <c r="V196" s="1">
+        <v>0</v>
+      </c>
+      <c r="W196" s="1">
+        <v>0</v>
+      </c>
+      <c r="X196" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y196" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z196" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA196" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB196" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A197" s="13" t="str">
+        <v>3z</v>
+      </c>
+      <c r="B197" s="1">
+        <v>0</v>
+      </c>
+      <c r="C197" s="1">
+        <v>0</v>
+      </c>
+      <c r="D197" s="1">
+        <v>0</v>
+      </c>
+      <c r="E197" s="1">
+        <v>0</v>
+      </c>
+      <c r="F197" s="1">
+        <v>0</v>
+      </c>
+      <c r="G197" s="1">
+        <v>0</v>
+      </c>
+      <c r="H197" s="1">
+        <v>2.0862461910941136E-11</v>
+      </c>
+      <c r="I197" s="1">
         <v>341905.92010540701</v>
       </c>
-      <c r="D119" s="1">
+      <c r="J197" s="1">
         <v>-1.6362715224267559E-11</v>
       </c>
-      <c r="E119" s="1">
-        <v>0</v>
-      </c>
-      <c r="F119" s="1">
-        <v>0</v>
-      </c>
-      <c r="G119" s="1">
-        <v>0</v>
-      </c>
-      <c r="H119" s="1">
-        <v>0</v>
-      </c>
-      <c r="I119" s="1">
-        <v>0</v>
-      </c>
-      <c r="J119" s="1">
-        <v>0</v>
-      </c>
-      <c r="K119" s="1">
-        <v>0</v>
-      </c>
-      <c r="L119" s="1">
-        <v>0</v>
-      </c>
-      <c r="M119" s="1">
-        <v>0</v>
-      </c>
-      <c r="N119" s="1">
-        <v>0</v>
-      </c>
-      <c r="O119" s="1">
-        <v>0</v>
-      </c>
-      <c r="P119" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="1">
-        <v>0</v>
-      </c>
-      <c r="R119" s="1">
-        <v>0</v>
-      </c>
-      <c r="S119" s="1">
-        <v>0</v>
-      </c>
-      <c r="T119" s="1">
-        <v>0</v>
-      </c>
-      <c r="U119" s="1">
-        <v>0</v>
-      </c>
-      <c r="V119" s="1">
-        <v>0</v>
-      </c>
-      <c r="W119" s="1">
-        <v>0</v>
-      </c>
-      <c r="X119" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y119" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB119" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A120" s="18" t="str">
-        <v>ϴ 1</v>
-      </c>
-      <c r="B120" s="1">
+      <c r="K197" s="1">
+        <v>0</v>
+      </c>
+      <c r="L197" s="1">
+        <v>0</v>
+      </c>
+      <c r="M197" s="1">
+        <v>0</v>
+      </c>
+      <c r="N197" s="1">
+        <v>0</v>
+      </c>
+      <c r="O197" s="1">
+        <v>0</v>
+      </c>
+      <c r="P197" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q197" s="1">
+        <v>0</v>
+      </c>
+      <c r="R197" s="1">
+        <v>0</v>
+      </c>
+      <c r="S197" s="1">
+        <v>0</v>
+      </c>
+      <c r="T197" s="1">
+        <v>0</v>
+      </c>
+      <c r="U197" s="1">
+        <v>0</v>
+      </c>
+      <c r="V197" s="1">
+        <v>0</v>
+      </c>
+      <c r="W197" s="1">
+        <v>0</v>
+      </c>
+      <c r="X197" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y197" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z197" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB197" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A198" s="13" t="str">
+        <v>ϴ 3</v>
+      </c>
+      <c r="B198" s="1">
+        <v>0</v>
+      </c>
+      <c r="C198" s="1">
+        <v>0</v>
+      </c>
+      <c r="D198" s="1">
+        <v>0</v>
+      </c>
+      <c r="E198" s="1">
+        <v>0</v>
+      </c>
+      <c r="F198" s="1">
+        <v>0</v>
+      </c>
+      <c r="G198" s="1">
+        <v>0</v>
+      </c>
+      <c r="H198" s="1">
         <v>267114.00008234923</v>
       </c>
-      <c r="C120" s="1">
+      <c r="I198" s="1">
         <v>-1.6362715224267559E-11</v>
       </c>
-      <c r="D120" s="1">
+      <c r="J198" s="1">
         <v>71230400.021959797</v>
       </c>
-      <c r="E120" s="1">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1">
-        <v>0</v>
-      </c>
-      <c r="G120" s="1">
-        <v>0</v>
-      </c>
-      <c r="H120" s="1">
-        <v>0</v>
-      </c>
-      <c r="I120" s="1">
-        <v>0</v>
-      </c>
-      <c r="J120" s="1">
-        <v>0</v>
-      </c>
-      <c r="K120" s="1">
-        <v>0</v>
-      </c>
-      <c r="L120" s="1">
-        <v>0</v>
-      </c>
-      <c r="M120" s="1">
-        <v>0</v>
-      </c>
-      <c r="N120" s="1">
-        <v>0</v>
-      </c>
-      <c r="O120" s="1">
-        <v>0</v>
-      </c>
-      <c r="P120" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q120" s="1">
-        <v>0</v>
-      </c>
-      <c r="R120" s="1">
-        <v>0</v>
-      </c>
-      <c r="S120" s="1">
-        <v>0</v>
-      </c>
-      <c r="T120" s="1">
-        <v>0</v>
-      </c>
-      <c r="U120" s="1">
-        <v>0</v>
-      </c>
-      <c r="V120" s="1">
-        <v>0</v>
-      </c>
-      <c r="W120" s="1">
-        <v>0</v>
-      </c>
-      <c r="X120" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y120" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z120" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA120" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB120" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A121" s="18" t="str">
-        <v>2x</v>
-      </c>
-      <c r="B121" s="1">
-        <v>0</v>
-      </c>
-      <c r="C121" s="1">
-        <v>0</v>
-      </c>
-      <c r="D121" s="1">
-        <v>0</v>
-      </c>
-      <c r="E121" s="1">
-        <v>0</v>
-      </c>
-      <c r="F121" s="1">
-        <v>0</v>
-      </c>
-      <c r="G121" s="1">
-        <v>0</v>
-      </c>
-      <c r="H121" s="1">
-        <v>0</v>
-      </c>
-      <c r="I121" s="1">
-        <v>0</v>
-      </c>
-      <c r="J121" s="1">
-        <v>0</v>
-      </c>
-      <c r="K121" s="1">
-        <v>0</v>
-      </c>
-      <c r="L121" s="1">
-        <v>0</v>
-      </c>
-      <c r="M121" s="1">
-        <v>0</v>
-      </c>
-      <c r="N121" s="1">
-        <v>0</v>
-      </c>
-      <c r="O121" s="1">
-        <v>0</v>
-      </c>
-      <c r="P121" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="1">
-        <v>0</v>
-      </c>
-      <c r="R121" s="1">
-        <v>0</v>
-      </c>
-      <c r="S121" s="1">
-        <v>0</v>
-      </c>
-      <c r="T121" s="1">
-        <v>0</v>
-      </c>
-      <c r="U121" s="1">
-        <v>0</v>
-      </c>
-      <c r="V121" s="1">
-        <v>0</v>
-      </c>
-      <c r="W121" s="1">
-        <v>0</v>
-      </c>
-      <c r="X121" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y121" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA121" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB121" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A122" s="18" t="str">
-        <v>2z</v>
-      </c>
-      <c r="B122" s="1">
-        <v>0</v>
-      </c>
-      <c r="C122" s="1">
-        <v>0</v>
-      </c>
-      <c r="D122" s="1">
-        <v>0</v>
-      </c>
-      <c r="E122" s="1">
-        <v>0</v>
-      </c>
-      <c r="F122" s="1">
-        <v>0</v>
-      </c>
-      <c r="G122" s="1">
-        <v>0</v>
-      </c>
-      <c r="H122" s="1">
-        <v>0</v>
-      </c>
-      <c r="I122" s="1">
-        <v>0</v>
-      </c>
-      <c r="J122" s="1">
-        <v>0</v>
-      </c>
-      <c r="K122" s="1">
-        <v>0</v>
-      </c>
-      <c r="L122" s="1">
-        <v>0</v>
-      </c>
-      <c r="M122" s="1">
-        <v>0</v>
-      </c>
-      <c r="N122" s="1">
-        <v>0</v>
-      </c>
-      <c r="O122" s="1">
-        <v>0</v>
-      </c>
-      <c r="P122" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q122" s="1">
-        <v>0</v>
-      </c>
-      <c r="R122" s="1">
-        <v>0</v>
-      </c>
-      <c r="S122" s="1">
-        <v>0</v>
-      </c>
-      <c r="T122" s="1">
-        <v>0</v>
-      </c>
-      <c r="U122" s="1">
-        <v>0</v>
-      </c>
-      <c r="V122" s="1">
-        <v>0</v>
-      </c>
-      <c r="W122" s="1">
-        <v>0</v>
-      </c>
-      <c r="X122" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y122" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB122" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A123" s="18" t="str">
-        <v>ϴ 2</v>
-      </c>
-      <c r="B123" s="1">
-        <v>0</v>
-      </c>
-      <c r="C123" s="1">
-        <v>0</v>
-      </c>
-      <c r="D123" s="1">
-        <v>0</v>
-      </c>
-      <c r="E123" s="1">
-        <v>0</v>
-      </c>
-      <c r="F123" s="1">
-        <v>0</v>
-      </c>
-      <c r="G123" s="1">
-        <v>0</v>
-      </c>
-      <c r="H123" s="1">
-        <v>0</v>
-      </c>
-      <c r="I123" s="1">
-        <v>0</v>
-      </c>
-      <c r="J123" s="1">
-        <v>0</v>
-      </c>
-      <c r="K123" s="1">
-        <v>0</v>
-      </c>
-      <c r="L123" s="1">
-        <v>0</v>
-      </c>
-      <c r="M123" s="1">
-        <v>0</v>
-      </c>
-      <c r="N123" s="1">
-        <v>0</v>
-      </c>
-      <c r="O123" s="1">
-        <v>0</v>
-      </c>
-      <c r="P123" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="1">
-        <v>0</v>
-      </c>
-      <c r="R123" s="1">
-        <v>0</v>
-      </c>
-      <c r="S123" s="1">
-        <v>0</v>
-      </c>
-      <c r="T123" s="1">
-        <v>0</v>
-      </c>
-      <c r="U123" s="1">
-        <v>0</v>
-      </c>
-      <c r="V123" s="1">
-        <v>0</v>
-      </c>
-      <c r="W123" s="1">
-        <v>0</v>
-      </c>
-      <c r="X123" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y123" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A124" s="18" t="str">
-        <v>3x</v>
-      </c>
-      <c r="B124" s="1">
-        <v>0</v>
-      </c>
-      <c r="C124" s="1">
-        <v>0</v>
-      </c>
-      <c r="D124" s="1">
-        <v>0</v>
-      </c>
-      <c r="E124" s="1">
-        <v>0</v>
-      </c>
-      <c r="F124" s="1">
-        <v>0</v>
-      </c>
-      <c r="G124" s="1">
-        <v>0</v>
-      </c>
-      <c r="H124" s="1">
-        <v>0</v>
-      </c>
-      <c r="I124" s="1">
-        <v>0</v>
-      </c>
-      <c r="J124" s="1">
-        <v>0</v>
-      </c>
-      <c r="K124" s="1">
-        <v>0</v>
-      </c>
-      <c r="L124" s="1">
-        <v>0</v>
-      </c>
-      <c r="M124" s="1">
-        <v>0</v>
-      </c>
-      <c r="N124" s="1">
-        <v>0</v>
-      </c>
-      <c r="O124" s="1">
-        <v>0</v>
-      </c>
-      <c r="P124" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="1">
-        <v>0</v>
-      </c>
-      <c r="R124" s="1">
-        <v>0</v>
-      </c>
-      <c r="S124" s="1">
-        <v>0</v>
-      </c>
-      <c r="T124" s="1">
-        <v>0</v>
-      </c>
-      <c r="U124" s="1">
-        <v>0</v>
-      </c>
-      <c r="V124" s="1">
-        <v>0</v>
-      </c>
-      <c r="W124" s="1">
-        <v>0</v>
-      </c>
-      <c r="X124" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y124" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A125" s="18" t="str">
-        <v>3z</v>
-      </c>
-      <c r="B125" s="1">
-        <v>0</v>
-      </c>
-      <c r="C125" s="1">
-        <v>0</v>
-      </c>
-      <c r="D125" s="1">
-        <v>0</v>
-      </c>
-      <c r="E125" s="1">
-        <v>0</v>
-      </c>
-      <c r="F125" s="1">
-        <v>0</v>
-      </c>
-      <c r="G125" s="1">
-        <v>0</v>
-      </c>
-      <c r="H125" s="1">
-        <v>0</v>
-      </c>
-      <c r="I125" s="1">
-        <v>0</v>
-      </c>
-      <c r="J125" s="1">
-        <v>0</v>
-      </c>
-      <c r="K125" s="1">
-        <v>0</v>
-      </c>
-      <c r="L125" s="1">
-        <v>0</v>
-      </c>
-      <c r="M125" s="1">
-        <v>0</v>
-      </c>
-      <c r="N125" s="1">
-        <v>0</v>
-      </c>
-      <c r="O125" s="1">
-        <v>0</v>
-      </c>
-      <c r="P125" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="1">
-        <v>0</v>
-      </c>
-      <c r="R125" s="1">
-        <v>0</v>
-      </c>
-      <c r="S125" s="1">
-        <v>0</v>
-      </c>
-      <c r="T125" s="1">
-        <v>0</v>
-      </c>
-      <c r="U125" s="1">
-        <v>0</v>
-      </c>
-      <c r="V125" s="1">
-        <v>0</v>
-      </c>
-      <c r="W125" s="1">
-        <v>0</v>
-      </c>
-      <c r="X125" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y125" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB125" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A126" s="18" t="str">
-        <v>ϴ 3</v>
-      </c>
-      <c r="B126" s="1">
-        <v>0</v>
-      </c>
-      <c r="C126" s="1">
-        <v>0</v>
-      </c>
-      <c r="D126" s="1">
-        <v>0</v>
-      </c>
-      <c r="E126" s="1">
-        <v>0</v>
-      </c>
-      <c r="F126" s="1">
-        <v>0</v>
-      </c>
-      <c r="G126" s="1">
-        <v>0</v>
-      </c>
-      <c r="H126" s="1">
-        <v>0</v>
-      </c>
-      <c r="I126" s="1">
-        <v>0</v>
-      </c>
-      <c r="J126" s="1">
-        <v>0</v>
-      </c>
-      <c r="K126" s="1">
-        <v>0</v>
-      </c>
-      <c r="L126" s="1">
-        <v>0</v>
-      </c>
-      <c r="M126" s="1">
-        <v>0</v>
-      </c>
-      <c r="N126" s="1">
-        <v>0</v>
-      </c>
-      <c r="O126" s="1">
-        <v>0</v>
-      </c>
-      <c r="P126" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="1">
-        <v>0</v>
-      </c>
-      <c r="R126" s="1">
-        <v>0</v>
-      </c>
-      <c r="S126" s="1">
-        <v>0</v>
-      </c>
-      <c r="T126" s="1">
-        <v>0</v>
-      </c>
-      <c r="U126" s="1">
-        <v>0</v>
-      </c>
-      <c r="V126" s="1">
-        <v>0</v>
-      </c>
-      <c r="W126" s="1">
-        <v>0</v>
-      </c>
-      <c r="X126" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y126" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB126" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A127" s="18" t="str">
+      <c r="K198" s="1">
+        <v>0</v>
+      </c>
+      <c r="L198" s="1">
+        <v>0</v>
+      </c>
+      <c r="M198" s="1">
+        <v>0</v>
+      </c>
+      <c r="N198" s="1">
+        <v>0</v>
+      </c>
+      <c r="O198" s="1">
+        <v>0</v>
+      </c>
+      <c r="P198" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q198" s="1">
+        <v>0</v>
+      </c>
+      <c r="R198" s="1">
+        <v>0</v>
+      </c>
+      <c r="S198" s="1">
+        <v>0</v>
+      </c>
+      <c r="T198" s="1">
+        <v>0</v>
+      </c>
+      <c r="U198" s="1">
+        <v>0</v>
+      </c>
+      <c r="V198" s="1">
+        <v>0</v>
+      </c>
+      <c r="W198" s="1">
+        <v>0</v>
+      </c>
+      <c r="X198" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y198" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z198" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA198" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB198" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A199" s="13" t="str">
         <v>4x</v>
       </c>
-      <c r="B127" s="1">
-        <v>0</v>
-      </c>
-      <c r="C127" s="1">
-        <v>0</v>
-      </c>
-      <c r="D127" s="1">
-        <v>0</v>
-      </c>
-      <c r="E127" s="1">
-        <v>0</v>
-      </c>
-      <c r="F127" s="1">
-        <v>0</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0</v>
-      </c>
-      <c r="H127" s="1">
-        <v>0</v>
-      </c>
-      <c r="I127" s="1">
-        <v>0</v>
-      </c>
-      <c r="J127" s="1">
-        <v>0</v>
-      </c>
-      <c r="K127" s="1">
-        <v>0</v>
-      </c>
-      <c r="L127" s="1">
-        <v>0</v>
-      </c>
-      <c r="M127" s="1">
-        <v>0</v>
-      </c>
-      <c r="N127" s="1">
-        <v>0</v>
-      </c>
-      <c r="O127" s="1">
-        <v>0</v>
-      </c>
-      <c r="P127" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q127" s="1">
-        <v>0</v>
-      </c>
-      <c r="R127" s="1">
-        <v>0</v>
-      </c>
-      <c r="S127" s="1">
-        <v>0</v>
-      </c>
-      <c r="T127" s="1">
-        <v>0</v>
-      </c>
-      <c r="U127" s="1">
-        <v>0</v>
-      </c>
-      <c r="V127" s="1">
-        <v>0</v>
-      </c>
-      <c r="W127" s="1">
-        <v>0</v>
-      </c>
-      <c r="X127" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y127" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z127" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA127" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB127" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A128" s="18" t="str">
+      <c r="B199" s="1">
+        <v>0</v>
+      </c>
+      <c r="C199" s="1">
+        <v>0</v>
+      </c>
+      <c r="D199" s="1">
+        <v>0</v>
+      </c>
+      <c r="E199" s="1">
+        <v>0</v>
+      </c>
+      <c r="F199" s="1">
+        <v>0</v>
+      </c>
+      <c r="G199" s="1">
+        <v>0</v>
+      </c>
+      <c r="H199" s="1">
+        <v>0</v>
+      </c>
+      <c r="I199" s="1">
+        <v>0</v>
+      </c>
+      <c r="J199" s="1">
+        <v>0</v>
+      </c>
+      <c r="K199" s="1">
+        <v>0</v>
+      </c>
+      <c r="L199" s="1">
+        <v>0</v>
+      </c>
+      <c r="M199" s="1">
+        <v>0</v>
+      </c>
+      <c r="N199" s="1">
+        <v>0</v>
+      </c>
+      <c r="O199" s="1">
+        <v>0</v>
+      </c>
+      <c r="P199" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q199" s="1">
+        <v>0</v>
+      </c>
+      <c r="R199" s="1">
+        <v>0</v>
+      </c>
+      <c r="S199" s="1">
+        <v>0</v>
+      </c>
+      <c r="T199" s="1">
+        <v>0</v>
+      </c>
+      <c r="U199" s="1">
+        <v>0</v>
+      </c>
+      <c r="V199" s="1">
+        <v>0</v>
+      </c>
+      <c r="W199" s="1">
+        <v>0</v>
+      </c>
+      <c r="X199" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y199" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A200" s="13" t="str">
         <v>4z</v>
       </c>
-      <c r="B128" s="1">
-        <v>0</v>
-      </c>
-      <c r="C128" s="1">
-        <v>0</v>
-      </c>
-      <c r="D128" s="1">
-        <v>0</v>
-      </c>
-      <c r="E128" s="1">
-        <v>0</v>
-      </c>
-      <c r="F128" s="1">
-        <v>0</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0</v>
-      </c>
-      <c r="H128" s="1">
-        <v>0</v>
-      </c>
-      <c r="I128" s="1">
-        <v>0</v>
-      </c>
-      <c r="J128" s="1">
-        <v>0</v>
-      </c>
-      <c r="K128" s="1">
-        <v>0</v>
-      </c>
-      <c r="L128" s="1">
-        <v>0</v>
-      </c>
-      <c r="M128" s="1">
-        <v>0</v>
-      </c>
-      <c r="N128" s="1">
-        <v>0</v>
-      </c>
-      <c r="O128" s="1">
-        <v>0</v>
-      </c>
-      <c r="P128" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="1">
-        <v>0</v>
-      </c>
-      <c r="R128" s="1">
-        <v>0</v>
-      </c>
-      <c r="S128" s="1">
-        <v>0</v>
-      </c>
-      <c r="T128" s="1">
-        <v>0</v>
-      </c>
-      <c r="U128" s="1">
-        <v>0</v>
-      </c>
-      <c r="V128" s="1">
-        <v>0</v>
-      </c>
-      <c r="W128" s="1">
-        <v>0</v>
-      </c>
-      <c r="X128" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y128" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z128" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA128" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB128" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A129" s="18" t="str">
+      <c r="B200" s="1">
+        <v>0</v>
+      </c>
+      <c r="C200" s="1">
+        <v>0</v>
+      </c>
+      <c r="D200" s="1">
+        <v>0</v>
+      </c>
+      <c r="E200" s="1">
+        <v>0</v>
+      </c>
+      <c r="F200" s="1">
+        <v>0</v>
+      </c>
+      <c r="G200" s="1">
+        <v>0</v>
+      </c>
+      <c r="H200" s="1">
+        <v>0</v>
+      </c>
+      <c r="I200" s="1">
+        <v>0</v>
+      </c>
+      <c r="J200" s="1">
+        <v>0</v>
+      </c>
+      <c r="K200" s="1">
+        <v>0</v>
+      </c>
+      <c r="L200" s="1">
+        <v>0</v>
+      </c>
+      <c r="M200" s="1">
+        <v>0</v>
+      </c>
+      <c r="N200" s="1">
+        <v>0</v>
+      </c>
+      <c r="O200" s="1">
+        <v>0</v>
+      </c>
+      <c r="P200" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q200" s="1">
+        <v>0</v>
+      </c>
+      <c r="R200" s="1">
+        <v>0</v>
+      </c>
+      <c r="S200" s="1">
+        <v>0</v>
+      </c>
+      <c r="T200" s="1">
+        <v>0</v>
+      </c>
+      <c r="U200" s="1">
+        <v>0</v>
+      </c>
+      <c r="V200" s="1">
+        <v>0</v>
+      </c>
+      <c r="W200" s="1">
+        <v>0</v>
+      </c>
+      <c r="X200" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A201" s="13" t="str">
         <v>ϴ 4</v>
       </c>
-      <c r="B129" s="1">
-        <v>0</v>
-      </c>
-      <c r="C129" s="1">
-        <v>0</v>
-      </c>
-      <c r="D129" s="1">
-        <v>0</v>
-      </c>
-      <c r="E129" s="1">
-        <v>0</v>
-      </c>
-      <c r="F129" s="1">
-        <v>0</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0</v>
-      </c>
-      <c r="H129" s="1">
-        <v>0</v>
-      </c>
-      <c r="I129" s="1">
-        <v>0</v>
-      </c>
-      <c r="J129" s="1">
-        <v>0</v>
-      </c>
-      <c r="K129" s="1">
-        <v>0</v>
-      </c>
-      <c r="L129" s="1">
-        <v>0</v>
-      </c>
-      <c r="M129" s="1">
-        <v>0</v>
-      </c>
-      <c r="N129" s="1">
-        <v>0</v>
-      </c>
-      <c r="O129" s="1">
-        <v>0</v>
-      </c>
-      <c r="P129" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="1">
-        <v>0</v>
-      </c>
-      <c r="R129" s="1">
-        <v>0</v>
-      </c>
-      <c r="S129" s="1">
-        <v>0</v>
-      </c>
-      <c r="T129" s="1">
-        <v>0</v>
-      </c>
-      <c r="U129" s="1">
-        <v>0</v>
-      </c>
-      <c r="V129" s="1">
-        <v>0</v>
-      </c>
-      <c r="W129" s="1">
-        <v>0</v>
-      </c>
-      <c r="X129" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y129" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB129" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A130" s="18" t="str">
+      <c r="B201" s="1">
+        <v>0</v>
+      </c>
+      <c r="C201" s="1">
+        <v>0</v>
+      </c>
+      <c r="D201" s="1">
+        <v>0</v>
+      </c>
+      <c r="E201" s="1">
+        <v>0</v>
+      </c>
+      <c r="F201" s="1">
+        <v>0</v>
+      </c>
+      <c r="G201" s="1">
+        <v>0</v>
+      </c>
+      <c r="H201" s="1">
+        <v>0</v>
+      </c>
+      <c r="I201" s="1">
+        <v>0</v>
+      </c>
+      <c r="J201" s="1">
+        <v>0</v>
+      </c>
+      <c r="K201" s="1">
+        <v>0</v>
+      </c>
+      <c r="L201" s="1">
+        <v>0</v>
+      </c>
+      <c r="M201" s="1">
+        <v>0</v>
+      </c>
+      <c r="N201" s="1">
+        <v>0</v>
+      </c>
+      <c r="O201" s="1">
+        <v>0</v>
+      </c>
+      <c r="P201" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q201" s="1">
+        <v>0</v>
+      </c>
+      <c r="R201" s="1">
+        <v>0</v>
+      </c>
+      <c r="S201" s="1">
+        <v>0</v>
+      </c>
+      <c r="T201" s="1">
+        <v>0</v>
+      </c>
+      <c r="U201" s="1">
+        <v>0</v>
+      </c>
+      <c r="V201" s="1">
+        <v>0</v>
+      </c>
+      <c r="W201" s="1">
+        <v>0</v>
+      </c>
+      <c r="X201" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y201" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z201" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA201" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB201" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A202" s="13" t="str">
         <v>5x</v>
       </c>
-      <c r="B130" s="1">
-        <v>0</v>
-      </c>
-      <c r="C130" s="1">
-        <v>0</v>
-      </c>
-      <c r="D130" s="1">
-        <v>0</v>
-      </c>
-      <c r="E130" s="1">
-        <v>0</v>
-      </c>
-      <c r="F130" s="1">
-        <v>0</v>
-      </c>
-      <c r="G130" s="1">
-        <v>0</v>
-      </c>
-      <c r="H130" s="1">
-        <v>0</v>
-      </c>
-      <c r="I130" s="1">
-        <v>0</v>
-      </c>
-      <c r="J130" s="1">
-        <v>0</v>
-      </c>
-      <c r="K130" s="1">
-        <v>0</v>
-      </c>
-      <c r="L130" s="1">
-        <v>0</v>
-      </c>
-      <c r="M130" s="1">
-        <v>0</v>
-      </c>
-      <c r="N130" s="1">
-        <v>0</v>
-      </c>
-      <c r="O130" s="1">
-        <v>0</v>
-      </c>
-      <c r="P130" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q130" s="1">
-        <v>0</v>
-      </c>
-      <c r="R130" s="1">
-        <v>0</v>
-      </c>
-      <c r="S130" s="1">
-        <v>0</v>
-      </c>
-      <c r="T130" s="1">
-        <v>0</v>
-      </c>
-      <c r="U130" s="1">
-        <v>0</v>
-      </c>
-      <c r="V130" s="1">
-        <v>0</v>
-      </c>
-      <c r="W130" s="1">
-        <v>0</v>
-      </c>
-      <c r="X130" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y130" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z130" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB130" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A131" s="18" t="str">
+      <c r="B202" s="1">
+        <v>0</v>
+      </c>
+      <c r="C202" s="1">
+        <v>0</v>
+      </c>
+      <c r="D202" s="1">
+        <v>0</v>
+      </c>
+      <c r="E202" s="1">
+        <v>0</v>
+      </c>
+      <c r="F202" s="1">
+        <v>0</v>
+      </c>
+      <c r="G202" s="1">
+        <v>0</v>
+      </c>
+      <c r="H202" s="1">
+        <v>0</v>
+      </c>
+      <c r="I202" s="1">
+        <v>0</v>
+      </c>
+      <c r="J202" s="1">
+        <v>0</v>
+      </c>
+      <c r="K202" s="1">
+        <v>0</v>
+      </c>
+      <c r="L202" s="1">
+        <v>0</v>
+      </c>
+      <c r="M202" s="1">
+        <v>0</v>
+      </c>
+      <c r="N202" s="1">
+        <v>0</v>
+      </c>
+      <c r="O202" s="1">
+        <v>0</v>
+      </c>
+      <c r="P202" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q202" s="1">
+        <v>0</v>
+      </c>
+      <c r="R202" s="1">
+        <v>0</v>
+      </c>
+      <c r="S202" s="1">
+        <v>0</v>
+      </c>
+      <c r="T202" s="1">
+        <v>0</v>
+      </c>
+      <c r="U202" s="1">
+        <v>0</v>
+      </c>
+      <c r="V202" s="1">
+        <v>0</v>
+      </c>
+      <c r="W202" s="1">
+        <v>0</v>
+      </c>
+      <c r="X202" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y202" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z202" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA202" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB202" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A203" s="13" t="str">
         <v>5z</v>
       </c>
-      <c r="B131" s="1">
-        <v>0</v>
-      </c>
-      <c r="C131" s="1">
-        <v>0</v>
-      </c>
-      <c r="D131" s="1">
-        <v>0</v>
-      </c>
-      <c r="E131" s="1">
-        <v>0</v>
-      </c>
-      <c r="F131" s="1">
-        <v>0</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0</v>
-      </c>
-      <c r="H131" s="1">
-        <v>0</v>
-      </c>
-      <c r="I131" s="1">
-        <v>0</v>
-      </c>
-      <c r="J131" s="1">
-        <v>0</v>
-      </c>
-      <c r="K131" s="1">
-        <v>0</v>
-      </c>
-      <c r="L131" s="1">
-        <v>0</v>
-      </c>
-      <c r="M131" s="1">
-        <v>0</v>
-      </c>
-      <c r="N131" s="1">
-        <v>0</v>
-      </c>
-      <c r="O131" s="1">
-        <v>0</v>
-      </c>
-      <c r="P131" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q131" s="1">
-        <v>0</v>
-      </c>
-      <c r="R131" s="1">
-        <v>0</v>
-      </c>
-      <c r="S131" s="1">
-        <v>0</v>
-      </c>
-      <c r="T131" s="1">
-        <v>0</v>
-      </c>
-      <c r="U131" s="1">
-        <v>0</v>
-      </c>
-      <c r="V131" s="1">
-        <v>0</v>
-      </c>
-      <c r="W131" s="1">
-        <v>0</v>
-      </c>
-      <c r="X131" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y131" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z131" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA131" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB131" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A132" s="18" t="str">
+      <c r="B203" s="1">
+        <v>0</v>
+      </c>
+      <c r="C203" s="1">
+        <v>0</v>
+      </c>
+      <c r="D203" s="1">
+        <v>0</v>
+      </c>
+      <c r="E203" s="1">
+        <v>0</v>
+      </c>
+      <c r="F203" s="1">
+        <v>0</v>
+      </c>
+      <c r="G203" s="1">
+        <v>0</v>
+      </c>
+      <c r="H203" s="1">
+        <v>0</v>
+      </c>
+      <c r="I203" s="1">
+        <v>0</v>
+      </c>
+      <c r="J203" s="1">
+        <v>0</v>
+      </c>
+      <c r="K203" s="1">
+        <v>0</v>
+      </c>
+      <c r="L203" s="1">
+        <v>0</v>
+      </c>
+      <c r="M203" s="1">
+        <v>0</v>
+      </c>
+      <c r="N203" s="1">
+        <v>0</v>
+      </c>
+      <c r="O203" s="1">
+        <v>0</v>
+      </c>
+      <c r="P203" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q203" s="1">
+        <v>0</v>
+      </c>
+      <c r="R203" s="1">
+        <v>0</v>
+      </c>
+      <c r="S203" s="1">
+        <v>0</v>
+      </c>
+      <c r="T203" s="1">
+        <v>0</v>
+      </c>
+      <c r="U203" s="1">
+        <v>0</v>
+      </c>
+      <c r="V203" s="1">
+        <v>0</v>
+      </c>
+      <c r="W203" s="1">
+        <v>0</v>
+      </c>
+      <c r="X203" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y203" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z203" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA203" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB203" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A204" s="13" t="str">
         <v>ϴ 5</v>
       </c>
-      <c r="B132" s="1">
-        <v>0</v>
-      </c>
-      <c r="C132" s="1">
-        <v>0</v>
-      </c>
-      <c r="D132" s="1">
-        <v>0</v>
-      </c>
-      <c r="E132" s="1">
-        <v>0</v>
-      </c>
-      <c r="F132" s="1">
-        <v>0</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0</v>
-      </c>
-      <c r="H132" s="1">
-        <v>0</v>
-      </c>
-      <c r="I132" s="1">
-        <v>0</v>
-      </c>
-      <c r="J132" s="1">
-        <v>0</v>
-      </c>
-      <c r="K132" s="1">
-        <v>0</v>
-      </c>
-      <c r="L132" s="1">
-        <v>0</v>
-      </c>
-      <c r="M132" s="1">
-        <v>0</v>
-      </c>
-      <c r="N132" s="1">
-        <v>0</v>
-      </c>
-      <c r="O132" s="1">
-        <v>0</v>
-      </c>
-      <c r="P132" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q132" s="1">
-        <v>0</v>
-      </c>
-      <c r="R132" s="1">
-        <v>0</v>
-      </c>
-      <c r="S132" s="1">
-        <v>0</v>
-      </c>
-      <c r="T132" s="1">
-        <v>0</v>
-      </c>
-      <c r="U132" s="1">
-        <v>0</v>
-      </c>
-      <c r="V132" s="1">
-        <v>0</v>
-      </c>
-      <c r="W132" s="1">
-        <v>0</v>
-      </c>
-      <c r="X132" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y132" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA132" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB132" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A133" s="18" t="str">
+      <c r="B204" s="1">
+        <v>0</v>
+      </c>
+      <c r="C204" s="1">
+        <v>0</v>
+      </c>
+      <c r="D204" s="1">
+        <v>0</v>
+      </c>
+      <c r="E204" s="1">
+        <v>0</v>
+      </c>
+      <c r="F204" s="1">
+        <v>0</v>
+      </c>
+      <c r="G204" s="1">
+        <v>0</v>
+      </c>
+      <c r="H204" s="1">
+        <v>0</v>
+      </c>
+      <c r="I204" s="1">
+        <v>0</v>
+      </c>
+      <c r="J204" s="1">
+        <v>0</v>
+      </c>
+      <c r="K204" s="1">
+        <v>0</v>
+      </c>
+      <c r="L204" s="1">
+        <v>0</v>
+      </c>
+      <c r="M204" s="1">
+        <v>0</v>
+      </c>
+      <c r="N204" s="1">
+        <v>0</v>
+      </c>
+      <c r="O204" s="1">
+        <v>0</v>
+      </c>
+      <c r="P204" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q204" s="1">
+        <v>0</v>
+      </c>
+      <c r="R204" s="1">
+        <v>0</v>
+      </c>
+      <c r="S204" s="1">
+        <v>0</v>
+      </c>
+      <c r="T204" s="1">
+        <v>0</v>
+      </c>
+      <c r="U204" s="1">
+        <v>0</v>
+      </c>
+      <c r="V204" s="1">
+        <v>0</v>
+      </c>
+      <c r="W204" s="1">
+        <v>0</v>
+      </c>
+      <c r="X204" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y204" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z204" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA204" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB204" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A205" s="13" t="str">
         <v>6x</v>
       </c>
-      <c r="B133" s="1">
-        <v>0</v>
-      </c>
-      <c r="C133" s="1">
-        <v>0</v>
-      </c>
-      <c r="D133" s="1">
-        <v>0</v>
-      </c>
-      <c r="E133" s="1">
-        <v>0</v>
-      </c>
-      <c r="F133" s="1">
-        <v>0</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0</v>
-      </c>
-      <c r="H133" s="1">
-        <v>0</v>
-      </c>
-      <c r="I133" s="1">
-        <v>0</v>
-      </c>
-      <c r="J133" s="1">
-        <v>0</v>
-      </c>
-      <c r="K133" s="1">
-        <v>0</v>
-      </c>
-      <c r="L133" s="1">
-        <v>0</v>
-      </c>
-      <c r="M133" s="1">
-        <v>0</v>
-      </c>
-      <c r="N133" s="1">
-        <v>0</v>
-      </c>
-      <c r="O133" s="1">
-        <v>0</v>
-      </c>
-      <c r="P133" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="1">
-        <v>0</v>
-      </c>
-      <c r="R133" s="1">
-        <v>0</v>
-      </c>
-      <c r="S133" s="1">
-        <v>0</v>
-      </c>
-      <c r="T133" s="1">
-        <v>0</v>
-      </c>
-      <c r="U133" s="1">
-        <v>0</v>
-      </c>
-      <c r="V133" s="1">
-        <v>0</v>
-      </c>
-      <c r="W133" s="1">
-        <v>0</v>
-      </c>
-      <c r="X133" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y133" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA133" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB133" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A134" s="18" t="str">
+      <c r="B205" s="1">
+        <v>0</v>
+      </c>
+      <c r="C205" s="1">
+        <v>0</v>
+      </c>
+      <c r="D205" s="1">
+        <v>0</v>
+      </c>
+      <c r="E205" s="1">
+        <v>0</v>
+      </c>
+      <c r="F205" s="1">
+        <v>0</v>
+      </c>
+      <c r="G205" s="1">
+        <v>0</v>
+      </c>
+      <c r="H205" s="1">
+        <v>0</v>
+      </c>
+      <c r="I205" s="1">
+        <v>0</v>
+      </c>
+      <c r="J205" s="1">
+        <v>0</v>
+      </c>
+      <c r="K205" s="1">
+        <v>0</v>
+      </c>
+      <c r="L205" s="1">
+        <v>0</v>
+      </c>
+      <c r="M205" s="1">
+        <v>0</v>
+      </c>
+      <c r="N205" s="1">
+        <v>0</v>
+      </c>
+      <c r="O205" s="1">
+        <v>0</v>
+      </c>
+      <c r="P205" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q205" s="1">
+        <v>0</v>
+      </c>
+      <c r="R205" s="1">
+        <v>0</v>
+      </c>
+      <c r="S205" s="1">
+        <v>0</v>
+      </c>
+      <c r="T205" s="1">
+        <v>0</v>
+      </c>
+      <c r="U205" s="1">
+        <v>0</v>
+      </c>
+      <c r="V205" s="1">
+        <v>0</v>
+      </c>
+      <c r="W205" s="1">
+        <v>0</v>
+      </c>
+      <c r="X205" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y205" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z205" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB205" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A206" s="13" t="str">
         <v>6z</v>
       </c>
-      <c r="B134" s="1">
-        <v>0</v>
-      </c>
-      <c r="C134" s="1">
-        <v>0</v>
-      </c>
-      <c r="D134" s="1">
-        <v>0</v>
-      </c>
-      <c r="E134" s="1">
-        <v>0</v>
-      </c>
-      <c r="F134" s="1">
-        <v>0</v>
-      </c>
-      <c r="G134" s="1">
-        <v>0</v>
-      </c>
-      <c r="H134" s="1">
-        <v>0</v>
-      </c>
-      <c r="I134" s="1">
-        <v>0</v>
-      </c>
-      <c r="J134" s="1">
-        <v>0</v>
-      </c>
-      <c r="K134" s="1">
-        <v>0</v>
-      </c>
-      <c r="L134" s="1">
-        <v>0</v>
-      </c>
-      <c r="M134" s="1">
-        <v>0</v>
-      </c>
-      <c r="N134" s="1">
-        <v>0</v>
-      </c>
-      <c r="O134" s="1">
-        <v>0</v>
-      </c>
-      <c r="P134" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q134" s="1">
-        <v>0</v>
-      </c>
-      <c r="R134" s="1">
-        <v>0</v>
-      </c>
-      <c r="S134" s="1">
-        <v>0</v>
-      </c>
-      <c r="T134" s="1">
-        <v>0</v>
-      </c>
-      <c r="U134" s="1">
-        <v>0</v>
-      </c>
-      <c r="V134" s="1">
-        <v>0</v>
-      </c>
-      <c r="W134" s="1">
-        <v>0</v>
-      </c>
-      <c r="X134" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y134" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA134" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB134" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A135" s="18" t="str">
+      <c r="B206" s="1">
+        <v>0</v>
+      </c>
+      <c r="C206" s="1">
+        <v>0</v>
+      </c>
+      <c r="D206" s="1">
+        <v>0</v>
+      </c>
+      <c r="E206" s="1">
+        <v>0</v>
+      </c>
+      <c r="F206" s="1">
+        <v>0</v>
+      </c>
+      <c r="G206" s="1">
+        <v>0</v>
+      </c>
+      <c r="H206" s="1">
+        <v>0</v>
+      </c>
+      <c r="I206" s="1">
+        <v>0</v>
+      </c>
+      <c r="J206" s="1">
+        <v>0</v>
+      </c>
+      <c r="K206" s="1">
+        <v>0</v>
+      </c>
+      <c r="L206" s="1">
+        <v>0</v>
+      </c>
+      <c r="M206" s="1">
+        <v>0</v>
+      </c>
+      <c r="N206" s="1">
+        <v>0</v>
+      </c>
+      <c r="O206" s="1">
+        <v>0</v>
+      </c>
+      <c r="P206" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q206" s="1">
+        <v>0</v>
+      </c>
+      <c r="R206" s="1">
+        <v>0</v>
+      </c>
+      <c r="S206" s="1">
+        <v>0</v>
+      </c>
+      <c r="T206" s="1">
+        <v>0</v>
+      </c>
+      <c r="U206" s="1">
+        <v>0</v>
+      </c>
+      <c r="V206" s="1">
+        <v>0</v>
+      </c>
+      <c r="W206" s="1">
+        <v>0</v>
+      </c>
+      <c r="X206" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A207" s="13" t="str">
         <v>ϴ 6</v>
       </c>
-      <c r="B135" s="1">
-        <v>0</v>
-      </c>
-      <c r="C135" s="1">
-        <v>0</v>
-      </c>
-      <c r="D135" s="1">
-        <v>0</v>
-      </c>
-      <c r="E135" s="1">
-        <v>0</v>
-      </c>
-      <c r="F135" s="1">
-        <v>0</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0</v>
-      </c>
-      <c r="H135" s="1">
-        <v>0</v>
-      </c>
-      <c r="I135" s="1">
-        <v>0</v>
-      </c>
-      <c r="J135" s="1">
-        <v>0</v>
-      </c>
-      <c r="K135" s="1">
-        <v>0</v>
-      </c>
-      <c r="L135" s="1">
-        <v>0</v>
-      </c>
-      <c r="M135" s="1">
-        <v>0</v>
-      </c>
-      <c r="N135" s="1">
-        <v>0</v>
-      </c>
-      <c r="O135" s="1">
-        <v>0</v>
-      </c>
-      <c r="P135" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q135" s="1">
-        <v>0</v>
-      </c>
-      <c r="R135" s="1">
-        <v>0</v>
-      </c>
-      <c r="S135" s="1">
-        <v>0</v>
-      </c>
-      <c r="T135" s="1">
-        <v>0</v>
-      </c>
-      <c r="U135" s="1">
-        <v>0</v>
-      </c>
-      <c r="V135" s="1">
-        <v>0</v>
-      </c>
-      <c r="W135" s="1">
-        <v>0</v>
-      </c>
-      <c r="X135" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y135" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA135" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB135" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A136" s="18" t="str">
+      <c r="B207" s="1">
+        <v>0</v>
+      </c>
+      <c r="C207" s="1">
+        <v>0</v>
+      </c>
+      <c r="D207" s="1">
+        <v>0</v>
+      </c>
+      <c r="E207" s="1">
+        <v>0</v>
+      </c>
+      <c r="F207" s="1">
+        <v>0</v>
+      </c>
+      <c r="G207" s="1">
+        <v>0</v>
+      </c>
+      <c r="H207" s="1">
+        <v>0</v>
+      </c>
+      <c r="I207" s="1">
+        <v>0</v>
+      </c>
+      <c r="J207" s="1">
+        <v>0</v>
+      </c>
+      <c r="K207" s="1">
+        <v>0</v>
+      </c>
+      <c r="L207" s="1">
+        <v>0</v>
+      </c>
+      <c r="M207" s="1">
+        <v>0</v>
+      </c>
+      <c r="N207" s="1">
+        <v>0</v>
+      </c>
+      <c r="O207" s="1">
+        <v>0</v>
+      </c>
+      <c r="P207" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q207" s="1">
+        <v>0</v>
+      </c>
+      <c r="R207" s="1">
+        <v>0</v>
+      </c>
+      <c r="S207" s="1">
+        <v>0</v>
+      </c>
+      <c r="T207" s="1">
+        <v>0</v>
+      </c>
+      <c r="U207" s="1">
+        <v>0</v>
+      </c>
+      <c r="V207" s="1">
+        <v>0</v>
+      </c>
+      <c r="W207" s="1">
+        <v>0</v>
+      </c>
+      <c r="X207" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A208" s="13" t="str">
         <v>ax</v>
       </c>
-      <c r="B136" s="1">
-        <v>0</v>
-      </c>
-      <c r="C136" s="1">
-        <v>0</v>
-      </c>
-      <c r="D136" s="1">
-        <v>0</v>
-      </c>
-      <c r="E136" s="1">
-        <v>0</v>
-      </c>
-      <c r="F136" s="1">
-        <v>0</v>
-      </c>
-      <c r="G136" s="1">
-        <v>0</v>
-      </c>
-      <c r="H136" s="1">
-        <v>0</v>
-      </c>
-      <c r="I136" s="1">
-        <v>0</v>
-      </c>
-      <c r="J136" s="1">
-        <v>0</v>
-      </c>
-      <c r="K136" s="1">
-        <v>0</v>
-      </c>
-      <c r="L136" s="1">
-        <v>0</v>
-      </c>
-      <c r="M136" s="1">
-        <v>0</v>
-      </c>
-      <c r="N136" s="1">
-        <v>0</v>
-      </c>
-      <c r="O136" s="1">
-        <v>0</v>
-      </c>
-      <c r="P136" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q136" s="1">
-        <v>0</v>
-      </c>
-      <c r="R136" s="1">
-        <v>0</v>
-      </c>
-      <c r="S136" s="1">
-        <v>0</v>
-      </c>
-      <c r="T136" s="1">
-        <v>0</v>
-      </c>
-      <c r="U136" s="1">
-        <v>0</v>
-      </c>
-      <c r="V136" s="1">
-        <v>0</v>
-      </c>
-      <c r="W136" s="1">
-        <v>0</v>
-      </c>
-      <c r="X136" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y136" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA136" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB136" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A137" s="18" t="str">
+      <c r="B208" s="1">
+        <v>0</v>
+      </c>
+      <c r="C208" s="1">
+        <v>0</v>
+      </c>
+      <c r="D208" s="1">
+        <v>0</v>
+      </c>
+      <c r="E208" s="1">
+        <v>0</v>
+      </c>
+      <c r="F208" s="1">
+        <v>0</v>
+      </c>
+      <c r="G208" s="1">
+        <v>0</v>
+      </c>
+      <c r="H208" s="1">
+        <v>0</v>
+      </c>
+      <c r="I208" s="1">
+        <v>0</v>
+      </c>
+      <c r="J208" s="1">
+        <v>0</v>
+      </c>
+      <c r="K208" s="1">
+        <v>0</v>
+      </c>
+      <c r="L208" s="1">
+        <v>0</v>
+      </c>
+      <c r="M208" s="1">
+        <v>0</v>
+      </c>
+      <c r="N208" s="1">
+        <v>0</v>
+      </c>
+      <c r="O208" s="1">
+        <v>0</v>
+      </c>
+      <c r="P208" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q208" s="1">
+        <v>0</v>
+      </c>
+      <c r="R208" s="1">
+        <v>0</v>
+      </c>
+      <c r="S208" s="1">
+        <v>0</v>
+      </c>
+      <c r="T208" s="1">
+        <v>0</v>
+      </c>
+      <c r="U208" s="1">
+        <v>0</v>
+      </c>
+      <c r="V208" s="1">
+        <v>0</v>
+      </c>
+      <c r="W208" s="1">
+        <v>0</v>
+      </c>
+      <c r="X208" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y208" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z208" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA208" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB208" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A209" s="13" t="str">
         <v>az</v>
       </c>
-      <c r="B137" s="1">
-        <v>0</v>
-      </c>
-      <c r="C137" s="1">
-        <v>0</v>
-      </c>
-      <c r="D137" s="1">
-        <v>0</v>
-      </c>
-      <c r="E137" s="1">
-        <v>0</v>
-      </c>
-      <c r="F137" s="1">
-        <v>0</v>
-      </c>
-      <c r="G137" s="1">
-        <v>0</v>
-      </c>
-      <c r="H137" s="1">
-        <v>0</v>
-      </c>
-      <c r="I137" s="1">
-        <v>0</v>
-      </c>
-      <c r="J137" s="1">
-        <v>0</v>
-      </c>
-      <c r="K137" s="1">
-        <v>0</v>
-      </c>
-      <c r="L137" s="1">
-        <v>0</v>
-      </c>
-      <c r="M137" s="1">
-        <v>0</v>
-      </c>
-      <c r="N137" s="1">
-        <v>0</v>
-      </c>
-      <c r="O137" s="1">
-        <v>0</v>
-      </c>
-      <c r="P137" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q137" s="1">
-        <v>0</v>
-      </c>
-      <c r="R137" s="1">
-        <v>0</v>
-      </c>
-      <c r="S137" s="1">
-        <v>0</v>
-      </c>
-      <c r="T137" s="1">
-        <v>0</v>
-      </c>
-      <c r="U137" s="1">
-        <v>0</v>
-      </c>
-      <c r="V137" s="1">
-        <v>0</v>
-      </c>
-      <c r="W137" s="1">
-        <v>0</v>
-      </c>
-      <c r="X137" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y137" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA137" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB137" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A138" s="18" t="str">
+      <c r="B209" s="1">
+        <v>0</v>
+      </c>
+      <c r="C209" s="1">
+        <v>0</v>
+      </c>
+      <c r="D209" s="1">
+        <v>0</v>
+      </c>
+      <c r="E209" s="1">
+        <v>0</v>
+      </c>
+      <c r="F209" s="1">
+        <v>0</v>
+      </c>
+      <c r="G209" s="1">
+        <v>0</v>
+      </c>
+      <c r="H209" s="1">
+        <v>0</v>
+      </c>
+      <c r="I209" s="1">
+        <v>0</v>
+      </c>
+      <c r="J209" s="1">
+        <v>0</v>
+      </c>
+      <c r="K209" s="1">
+        <v>0</v>
+      </c>
+      <c r="L209" s="1">
+        <v>0</v>
+      </c>
+      <c r="M209" s="1">
+        <v>0</v>
+      </c>
+      <c r="N209" s="1">
+        <v>0</v>
+      </c>
+      <c r="O209" s="1">
+        <v>0</v>
+      </c>
+      <c r="P209" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q209" s="1">
+        <v>0</v>
+      </c>
+      <c r="R209" s="1">
+        <v>0</v>
+      </c>
+      <c r="S209" s="1">
+        <v>0</v>
+      </c>
+      <c r="T209" s="1">
+        <v>0</v>
+      </c>
+      <c r="U209" s="1">
+        <v>0</v>
+      </c>
+      <c r="V209" s="1">
+        <v>0</v>
+      </c>
+      <c r="W209" s="1">
+        <v>0</v>
+      </c>
+      <c r="X209" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y209" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA209" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB209" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A210" s="13" t="str">
         <v>ϴ a</v>
       </c>
-      <c r="B138" s="1">
-        <v>0</v>
-      </c>
-      <c r="C138" s="1">
-        <v>0</v>
-      </c>
-      <c r="D138" s="1">
-        <v>0</v>
-      </c>
-      <c r="E138" s="1">
-        <v>0</v>
-      </c>
-      <c r="F138" s="1">
-        <v>0</v>
-      </c>
-      <c r="G138" s="1">
-        <v>0</v>
-      </c>
-      <c r="H138" s="1">
-        <v>0</v>
-      </c>
-      <c r="I138" s="1">
-        <v>0</v>
-      </c>
-      <c r="J138" s="1">
-        <v>0</v>
-      </c>
-      <c r="K138" s="1">
-        <v>0</v>
-      </c>
-      <c r="L138" s="1">
-        <v>0</v>
-      </c>
-      <c r="M138" s="1">
-        <v>0</v>
-      </c>
-      <c r="N138" s="1">
-        <v>0</v>
-      </c>
-      <c r="O138" s="1">
-        <v>0</v>
-      </c>
-      <c r="P138" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q138" s="1">
-        <v>0</v>
-      </c>
-      <c r="R138" s="1">
-        <v>0</v>
-      </c>
-      <c r="S138" s="1">
-        <v>0</v>
-      </c>
-      <c r="T138" s="1">
-        <v>0</v>
-      </c>
-      <c r="U138" s="1">
-        <v>0</v>
-      </c>
-      <c r="V138" s="1">
-        <v>0</v>
-      </c>
-      <c r="W138" s="1">
-        <v>0</v>
-      </c>
-      <c r="X138" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y138" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z138" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA138" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB138" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A139" s="18" t="str">
+      <c r="B210" s="1">
+        <v>0</v>
+      </c>
+      <c r="C210" s="1">
+        <v>0</v>
+      </c>
+      <c r="D210" s="1">
+        <v>0</v>
+      </c>
+      <c r="E210" s="1">
+        <v>0</v>
+      </c>
+      <c r="F210" s="1">
+        <v>0</v>
+      </c>
+      <c r="G210" s="1">
+        <v>0</v>
+      </c>
+      <c r="H210" s="1">
+        <v>0</v>
+      </c>
+      <c r="I210" s="1">
+        <v>0</v>
+      </c>
+      <c r="J210" s="1">
+        <v>0</v>
+      </c>
+      <c r="K210" s="1">
+        <v>0</v>
+      </c>
+      <c r="L210" s="1">
+        <v>0</v>
+      </c>
+      <c r="M210" s="1">
+        <v>0</v>
+      </c>
+      <c r="N210" s="1">
+        <v>0</v>
+      </c>
+      <c r="O210" s="1">
+        <v>0</v>
+      </c>
+      <c r="P210" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q210" s="1">
+        <v>0</v>
+      </c>
+      <c r="R210" s="1">
+        <v>0</v>
+      </c>
+      <c r="S210" s="1">
+        <v>0</v>
+      </c>
+      <c r="T210" s="1">
+        <v>0</v>
+      </c>
+      <c r="U210" s="1">
+        <v>0</v>
+      </c>
+      <c r="V210" s="1">
+        <v>0</v>
+      </c>
+      <c r="W210" s="1">
+        <v>0</v>
+      </c>
+      <c r="X210" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y210" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z210" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA210" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB210" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A211" s="13" t="str">
         <v>bx</v>
       </c>
-      <c r="B139" s="1">
-        <v>0</v>
-      </c>
-      <c r="C139" s="1">
-        <v>0</v>
-      </c>
-      <c r="D139" s="1">
-        <v>0</v>
-      </c>
-      <c r="E139" s="1">
-        <v>0</v>
-      </c>
-      <c r="F139" s="1">
-        <v>0</v>
-      </c>
-      <c r="G139" s="1">
-        <v>0</v>
-      </c>
-      <c r="H139" s="1">
-        <v>0</v>
-      </c>
-      <c r="I139" s="1">
-        <v>0</v>
-      </c>
-      <c r="J139" s="1">
-        <v>0</v>
-      </c>
-      <c r="K139" s="1">
-        <v>0</v>
-      </c>
-      <c r="L139" s="1">
-        <v>0</v>
-      </c>
-      <c r="M139" s="1">
-        <v>0</v>
-      </c>
-      <c r="N139" s="1">
-        <v>0</v>
-      </c>
-      <c r="O139" s="1">
-        <v>0</v>
-      </c>
-      <c r="P139" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q139" s="1">
-        <v>0</v>
-      </c>
-      <c r="R139" s="1">
-        <v>0</v>
-      </c>
-      <c r="S139" s="1">
-        <v>0</v>
-      </c>
-      <c r="T139" s="1">
-        <v>0</v>
-      </c>
-      <c r="U139" s="1">
-        <v>0</v>
-      </c>
-      <c r="V139" s="1">
-        <v>0</v>
-      </c>
-      <c r="W139" s="1">
-        <v>0</v>
-      </c>
-      <c r="X139" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y139" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z139" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA139" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB139" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A140" s="18" t="str">
+      <c r="B211" s="1">
+        <v>0</v>
+      </c>
+      <c r="C211" s="1">
+        <v>0</v>
+      </c>
+      <c r="D211" s="1">
+        <v>0</v>
+      </c>
+      <c r="E211" s="1">
+        <v>0</v>
+      </c>
+      <c r="F211" s="1">
+        <v>0</v>
+      </c>
+      <c r="G211" s="1">
+        <v>0</v>
+      </c>
+      <c r="H211" s="1">
+        <v>0</v>
+      </c>
+      <c r="I211" s="1">
+        <v>0</v>
+      </c>
+      <c r="J211" s="1">
+        <v>0</v>
+      </c>
+      <c r="K211" s="1">
+        <v>0</v>
+      </c>
+      <c r="L211" s="1">
+        <v>0</v>
+      </c>
+      <c r="M211" s="1">
+        <v>0</v>
+      </c>
+      <c r="N211" s="1">
+        <v>0</v>
+      </c>
+      <c r="O211" s="1">
+        <v>0</v>
+      </c>
+      <c r="P211" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q211" s="1">
+        <v>0</v>
+      </c>
+      <c r="R211" s="1">
+        <v>0</v>
+      </c>
+      <c r="S211" s="1">
+        <v>0</v>
+      </c>
+      <c r="T211" s="1">
+        <v>0</v>
+      </c>
+      <c r="U211" s="1">
+        <v>0</v>
+      </c>
+      <c r="V211" s="1">
+        <v>0</v>
+      </c>
+      <c r="W211" s="1">
+        <v>0</v>
+      </c>
+      <c r="X211" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y211" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z211" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA211" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB211" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A212" s="13" t="str">
         <v>bz</v>
       </c>
-      <c r="B140" s="1">
-        <v>0</v>
-      </c>
-      <c r="C140" s="1">
-        <v>0</v>
-      </c>
-      <c r="D140" s="1">
-        <v>0</v>
-      </c>
-      <c r="E140" s="1">
-        <v>0</v>
-      </c>
-      <c r="F140" s="1">
-        <v>0</v>
-      </c>
-      <c r="G140" s="1">
-        <v>0</v>
-      </c>
-      <c r="H140" s="1">
-        <v>0</v>
-      </c>
-      <c r="I140" s="1">
-        <v>0</v>
-      </c>
-      <c r="J140" s="1">
-        <v>0</v>
-      </c>
-      <c r="K140" s="1">
-        <v>0</v>
-      </c>
-      <c r="L140" s="1">
-        <v>0</v>
-      </c>
-      <c r="M140" s="1">
-        <v>0</v>
-      </c>
-      <c r="N140" s="1">
-        <v>0</v>
-      </c>
-      <c r="O140" s="1">
-        <v>0</v>
-      </c>
-      <c r="P140" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="1">
-        <v>0</v>
-      </c>
-      <c r="R140" s="1">
-        <v>0</v>
-      </c>
-      <c r="S140" s="1">
-        <v>0</v>
-      </c>
-      <c r="T140" s="1">
-        <v>0</v>
-      </c>
-      <c r="U140" s="1">
-        <v>0</v>
-      </c>
-      <c r="V140" s="1">
-        <v>0</v>
-      </c>
-      <c r="W140" s="1">
-        <v>0</v>
-      </c>
-      <c r="X140" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y140" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z140" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA140" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB140" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A141" s="18" t="str">
+      <c r="B212" s="1">
+        <v>0</v>
+      </c>
+      <c r="C212" s="1">
+        <v>0</v>
+      </c>
+      <c r="D212" s="1">
+        <v>0</v>
+      </c>
+      <c r="E212" s="1">
+        <v>0</v>
+      </c>
+      <c r="F212" s="1">
+        <v>0</v>
+      </c>
+      <c r="G212" s="1">
+        <v>0</v>
+      </c>
+      <c r="H212" s="1">
+        <v>0</v>
+      </c>
+      <c r="I212" s="1">
+        <v>0</v>
+      </c>
+      <c r="J212" s="1">
+        <v>0</v>
+      </c>
+      <c r="K212" s="1">
+        <v>0</v>
+      </c>
+      <c r="L212" s="1">
+        <v>0</v>
+      </c>
+      <c r="M212" s="1">
+        <v>0</v>
+      </c>
+      <c r="N212" s="1">
+        <v>0</v>
+      </c>
+      <c r="O212" s="1">
+        <v>0</v>
+      </c>
+      <c r="P212" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q212" s="1">
+        <v>0</v>
+      </c>
+      <c r="R212" s="1">
+        <v>0</v>
+      </c>
+      <c r="S212" s="1">
+        <v>0</v>
+      </c>
+      <c r="T212" s="1">
+        <v>0</v>
+      </c>
+      <c r="U212" s="1">
+        <v>0</v>
+      </c>
+      <c r="V212" s="1">
+        <v>0</v>
+      </c>
+      <c r="W212" s="1">
+        <v>0</v>
+      </c>
+      <c r="X212" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y212" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z212" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA212" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB212" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A213" s="13" t="str">
         <v>ϴ b</v>
       </c>
-      <c r="B141" s="1">
-        <v>0</v>
-      </c>
-      <c r="C141" s="1">
-        <v>0</v>
-      </c>
-      <c r="D141" s="1">
-        <v>0</v>
-      </c>
-      <c r="E141" s="1">
-        <v>0</v>
-      </c>
-      <c r="F141" s="1">
-        <v>0</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0</v>
-      </c>
-      <c r="H141" s="1">
-        <v>0</v>
-      </c>
-      <c r="I141" s="1">
-        <v>0</v>
-      </c>
-      <c r="J141" s="1">
-        <v>0</v>
-      </c>
-      <c r="K141" s="1">
-        <v>0</v>
-      </c>
-      <c r="L141" s="1">
-        <v>0</v>
-      </c>
-      <c r="M141" s="1">
-        <v>0</v>
-      </c>
-      <c r="N141" s="1">
-        <v>0</v>
-      </c>
-      <c r="O141" s="1">
-        <v>0</v>
-      </c>
-      <c r="P141" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q141" s="1">
-        <v>0</v>
-      </c>
-      <c r="R141" s="1">
-        <v>0</v>
-      </c>
-      <c r="S141" s="1">
-        <v>0</v>
-      </c>
-      <c r="T141" s="1">
-        <v>0</v>
-      </c>
-      <c r="U141" s="1">
-        <v>0</v>
-      </c>
-      <c r="V141" s="1">
-        <v>0</v>
-      </c>
-      <c r="W141" s="1">
-        <v>0</v>
-      </c>
-      <c r="X141" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y141" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z141" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA141" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB141" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A142" s="18" t="str">
+      <c r="B213" s="1">
+        <v>0</v>
+      </c>
+      <c r="C213" s="1">
+        <v>0</v>
+      </c>
+      <c r="D213" s="1">
+        <v>0</v>
+      </c>
+      <c r="E213" s="1">
+        <v>0</v>
+      </c>
+      <c r="F213" s="1">
+        <v>0</v>
+      </c>
+      <c r="G213" s="1">
+        <v>0</v>
+      </c>
+      <c r="H213" s="1">
+        <v>0</v>
+      </c>
+      <c r="I213" s="1">
+        <v>0</v>
+      </c>
+      <c r="J213" s="1">
+        <v>0</v>
+      </c>
+      <c r="K213" s="1">
+        <v>0</v>
+      </c>
+      <c r="L213" s="1">
+        <v>0</v>
+      </c>
+      <c r="M213" s="1">
+        <v>0</v>
+      </c>
+      <c r="N213" s="1">
+        <v>0</v>
+      </c>
+      <c r="O213" s="1">
+        <v>0</v>
+      </c>
+      <c r="P213" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q213" s="1">
+        <v>0</v>
+      </c>
+      <c r="R213" s="1">
+        <v>0</v>
+      </c>
+      <c r="S213" s="1">
+        <v>0</v>
+      </c>
+      <c r="T213" s="1">
+        <v>0</v>
+      </c>
+      <c r="U213" s="1">
+        <v>0</v>
+      </c>
+      <c r="V213" s="1">
+        <v>0</v>
+      </c>
+      <c r="W213" s="1">
+        <v>0</v>
+      </c>
+      <c r="X213" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y213" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z213" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA213" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB213" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A214" s="13" t="str">
         <v>cx</v>
       </c>
-      <c r="B142" s="1">
-        <v>0</v>
-      </c>
-      <c r="C142" s="1">
-        <v>0</v>
-      </c>
-      <c r="D142" s="1">
-        <v>0</v>
-      </c>
-      <c r="E142" s="1">
-        <v>0</v>
-      </c>
-      <c r="F142" s="1">
-        <v>0</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0</v>
-      </c>
-      <c r="H142" s="1">
-        <v>0</v>
-      </c>
-      <c r="I142" s="1">
-        <v>0</v>
-      </c>
-      <c r="J142" s="1">
-        <v>0</v>
-      </c>
-      <c r="K142" s="1">
-        <v>0</v>
-      </c>
-      <c r="L142" s="1">
-        <v>0</v>
-      </c>
-      <c r="M142" s="1">
-        <v>0</v>
-      </c>
-      <c r="N142" s="1">
-        <v>0</v>
-      </c>
-      <c r="O142" s="1">
-        <v>0</v>
-      </c>
-      <c r="P142" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="1">
-        <v>0</v>
-      </c>
-      <c r="R142" s="1">
-        <v>0</v>
-      </c>
-      <c r="S142" s="1">
-        <v>0</v>
-      </c>
-      <c r="T142" s="1">
-        <v>0</v>
-      </c>
-      <c r="U142" s="1">
-        <v>0</v>
-      </c>
-      <c r="V142" s="1">
-        <v>0</v>
-      </c>
-      <c r="W142" s="1">
-        <v>0</v>
-      </c>
-      <c r="X142" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y142" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z142" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA142" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB142" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A143" s="18" t="str">
+      <c r="B214" s="1">
+        <v>0</v>
+      </c>
+      <c r="C214" s="1">
+        <v>0</v>
+      </c>
+      <c r="D214" s="1">
+        <v>0</v>
+      </c>
+      <c r="E214" s="1">
+        <v>0</v>
+      </c>
+      <c r="F214" s="1">
+        <v>0</v>
+      </c>
+      <c r="G214" s="1">
+        <v>0</v>
+      </c>
+      <c r="H214" s="1">
+        <v>0</v>
+      </c>
+      <c r="I214" s="1">
+        <v>0</v>
+      </c>
+      <c r="J214" s="1">
+        <v>0</v>
+      </c>
+      <c r="K214" s="1">
+        <v>0</v>
+      </c>
+      <c r="L214" s="1">
+        <v>0</v>
+      </c>
+      <c r="M214" s="1">
+        <v>0</v>
+      </c>
+      <c r="N214" s="1">
+        <v>0</v>
+      </c>
+      <c r="O214" s="1">
+        <v>0</v>
+      </c>
+      <c r="P214" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q214" s="1">
+        <v>0</v>
+      </c>
+      <c r="R214" s="1">
+        <v>0</v>
+      </c>
+      <c r="S214" s="1">
+        <v>0</v>
+      </c>
+      <c r="T214" s="1">
+        <v>0</v>
+      </c>
+      <c r="U214" s="1">
+        <v>0</v>
+      </c>
+      <c r="V214" s="1">
+        <v>0</v>
+      </c>
+      <c r="W214" s="1">
+        <v>0</v>
+      </c>
+      <c r="X214" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y214" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z214" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA214" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB214" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A215" s="13" t="str">
         <v>cz</v>
       </c>
-      <c r="B143" s="1">
-        <v>0</v>
-      </c>
-      <c r="C143" s="1">
-        <v>0</v>
-      </c>
-      <c r="D143" s="1">
-        <v>0</v>
-      </c>
-      <c r="E143" s="1">
-        <v>0</v>
-      </c>
-      <c r="F143" s="1">
-        <v>0</v>
-      </c>
-      <c r="G143" s="1">
-        <v>0</v>
-      </c>
-      <c r="H143" s="1">
-        <v>0</v>
-      </c>
-      <c r="I143" s="1">
-        <v>0</v>
-      </c>
-      <c r="J143" s="1">
-        <v>0</v>
-      </c>
-      <c r="K143" s="1">
-        <v>0</v>
-      </c>
-      <c r="L143" s="1">
-        <v>0</v>
-      </c>
-      <c r="M143" s="1">
-        <v>0</v>
-      </c>
-      <c r="N143" s="1">
-        <v>0</v>
-      </c>
-      <c r="O143" s="1">
-        <v>0</v>
-      </c>
-      <c r="P143" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q143" s="1">
-        <v>0</v>
-      </c>
-      <c r="R143" s="1">
-        <v>0</v>
-      </c>
-      <c r="S143" s="1">
-        <v>0</v>
-      </c>
-      <c r="T143" s="1">
-        <v>0</v>
-      </c>
-      <c r="U143" s="1">
-        <v>0</v>
-      </c>
-      <c r="V143" s="1">
-        <v>0</v>
-      </c>
-      <c r="W143" s="1">
-        <v>0</v>
-      </c>
-      <c r="X143" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y143" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z143" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA143" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB143" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A144" s="18" t="str">
+      <c r="B215" s="1">
+        <v>0</v>
+      </c>
+      <c r="C215" s="1">
+        <v>0</v>
+      </c>
+      <c r="D215" s="1">
+        <v>0</v>
+      </c>
+      <c r="E215" s="1">
+        <v>0</v>
+      </c>
+      <c r="F215" s="1">
+        <v>0</v>
+      </c>
+      <c r="G215" s="1">
+        <v>0</v>
+      </c>
+      <c r="H215" s="1">
+        <v>0</v>
+      </c>
+      <c r="I215" s="1">
+        <v>0</v>
+      </c>
+      <c r="J215" s="1">
+        <v>0</v>
+      </c>
+      <c r="K215" s="1">
+        <v>0</v>
+      </c>
+      <c r="L215" s="1">
+        <v>0</v>
+      </c>
+      <c r="M215" s="1">
+        <v>0</v>
+      </c>
+      <c r="N215" s="1">
+        <v>0</v>
+      </c>
+      <c r="O215" s="1">
+        <v>0</v>
+      </c>
+      <c r="P215" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q215" s="1">
+        <v>0</v>
+      </c>
+      <c r="R215" s="1">
+        <v>0</v>
+      </c>
+      <c r="S215" s="1">
+        <v>0</v>
+      </c>
+      <c r="T215" s="1">
+        <v>0</v>
+      </c>
+      <c r="U215" s="1">
+        <v>0</v>
+      </c>
+      <c r="V215" s="1">
+        <v>0</v>
+      </c>
+      <c r="W215" s="1">
+        <v>0</v>
+      </c>
+      <c r="X215" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y215" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z215" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA215" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB215" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A216" s="13" t="str">
         <v>ϴ c</v>
       </c>
-      <c r="B144" s="1">
-        <v>0</v>
-      </c>
-      <c r="C144" s="1">
-        <v>0</v>
-      </c>
-      <c r="D144" s="1">
-        <v>0</v>
-      </c>
-      <c r="E144" s="1">
-        <v>0</v>
-      </c>
-      <c r="F144" s="1">
-        <v>0</v>
-      </c>
-      <c r="G144" s="1">
-        <v>0</v>
-      </c>
-      <c r="H144" s="1">
-        <v>0</v>
-      </c>
-      <c r="I144" s="1">
-        <v>0</v>
-      </c>
-      <c r="J144" s="1">
-        <v>0</v>
-      </c>
-      <c r="K144" s="1">
-        <v>0</v>
-      </c>
-      <c r="L144" s="1">
-        <v>0</v>
-      </c>
-      <c r="M144" s="1">
-        <v>0</v>
-      </c>
-      <c r="N144" s="1">
-        <v>0</v>
-      </c>
-      <c r="O144" s="1">
-        <v>0</v>
-      </c>
-      <c r="P144" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q144" s="1">
-        <v>0</v>
-      </c>
-      <c r="R144" s="1">
-        <v>0</v>
-      </c>
-      <c r="S144" s="1">
-        <v>0</v>
-      </c>
-      <c r="T144" s="1">
-        <v>0</v>
-      </c>
-      <c r="U144" s="1">
-        <v>0</v>
-      </c>
-      <c r="V144" s="1">
-        <v>0</v>
-      </c>
-      <c r="W144" s="1">
-        <v>0</v>
-      </c>
-      <c r="X144" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y144" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z144" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB144" s="1">
+      <c r="B216" s="1">
+        <v>0</v>
+      </c>
+      <c r="C216" s="1">
+        <v>0</v>
+      </c>
+      <c r="D216" s="1">
+        <v>0</v>
+      </c>
+      <c r="E216" s="1">
+        <v>0</v>
+      </c>
+      <c r="F216" s="1">
+        <v>0</v>
+      </c>
+      <c r="G216" s="1">
+        <v>0</v>
+      </c>
+      <c r="H216" s="1">
+        <v>0</v>
+      </c>
+      <c r="I216" s="1">
+        <v>0</v>
+      </c>
+      <c r="J216" s="1">
+        <v>0</v>
+      </c>
+      <c r="K216" s="1">
+        <v>0</v>
+      </c>
+      <c r="L216" s="1">
+        <v>0</v>
+      </c>
+      <c r="M216" s="1">
+        <v>0</v>
+      </c>
+      <c r="N216" s="1">
+        <v>0</v>
+      </c>
+      <c r="O216" s="1">
+        <v>0</v>
+      </c>
+      <c r="P216" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q216" s="1">
+        <v>0</v>
+      </c>
+      <c r="R216" s="1">
+        <v>0</v>
+      </c>
+      <c r="S216" s="1">
+        <v>0</v>
+      </c>
+      <c r="T216" s="1">
+        <v>0</v>
+      </c>
+      <c r="U216" s="1">
+        <v>0</v>
+      </c>
+      <c r="V216" s="1">
+        <v>0</v>
+      </c>
+      <c r="W216" s="1">
+        <v>0</v>
+      </c>
+      <c r="X216" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y216" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB216" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="25">
+    <mergeCell ref="A161:G161"/>
+    <mergeCell ref="H163:I168"/>
+    <mergeCell ref="A170:J170"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="I171:J171"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="A147:J147"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
     <mergeCell ref="A75:J75"/>
     <mergeCell ref="A89:G89"/>
     <mergeCell ref="H91:I96"/>
@@ -7309,15 +10628,6 @@
     <mergeCell ref="E99:F99"/>
     <mergeCell ref="G99:H99"/>
     <mergeCell ref="I99:J99"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="H19:I24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
